--- a/tools/format-rd-tracker.xlsx
+++ b/tools/format-rd-tracker.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Post Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Format Scorecard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Seeding Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="60-Day Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Post Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Format Scorecard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Seeding Tracker" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="ddd dd mmm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="ddd dd mmm yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +84,13 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +110,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF3EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F1E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +190,29 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -772,6 +814,5907 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H215"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>60-Day Posting Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>191 original pieces in 60 days. Each one cross-posts to Instagram Reels, TikTok, YouTube Shorts and Facebook Reels — 4x the reach for no extra filming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Start date (edit this — every date below follows from it):</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Shoot batch</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Posted?</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="25">
+        <f>IF($E$3="","",$E$3+A6-1)</f>
+        <v/>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr"/>
+      <c r="H6" s="26" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="29">
+        <f>IF($E$3="","",$E$3+A7-1)</f>
+        <v/>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr"/>
+      <c r="H7" s="30" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25">
+        <f>IF($E$3="","",$E$3+A8-1)</f>
+        <v/>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr"/>
+      <c r="H8" s="26" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="25">
+        <f>IF($E$3="","",$E$3+A9-1)</f>
+        <v/>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr"/>
+      <c r="H9" s="26" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="25">
+        <f>IF($E$3="","",$E$3+A10-1)</f>
+        <v/>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr"/>
+      <c r="H10" s="26" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="29">
+        <f>IF($E$3="","",$E$3+A11-1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr"/>
+      <c r="H11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="25">
+        <f>IF($E$3="","",$E$3+A12-1)</f>
+        <v/>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr"/>
+      <c r="H12" s="26" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="29">
+        <f>IF($E$3="","",$E$3+A13-1)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr"/>
+      <c r="H13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="25">
+        <f>IF($E$3="","",$E$3+A14-1)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr"/>
+      <c r="H14" s="26" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="29">
+        <f>IF($E$3="","",$E$3+A15-1)</f>
+        <v/>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="inlineStr"/>
+      <c r="H15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="29">
+        <f>IF($E$3="","",$E$3+A16-1)</f>
+        <v/>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="inlineStr"/>
+      <c r="H16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="25">
+        <f>IF($E$3="","",$E$3+A17-1)</f>
+        <v/>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr"/>
+      <c r="H17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="29">
+        <f>IF($E$3="","",$E$3+A18-1)</f>
+        <v/>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr"/>
+      <c r="H18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="29">
+        <f>IF($E$3="","",$E$3+A19-1)</f>
+        <v/>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr"/>
+      <c r="H19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="25">
+        <f>IF($E$3="","",$E$3+A20-1)</f>
+        <v/>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr"/>
+      <c r="H20" s="26" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="29">
+        <f>IF($E$3="","",$E$3+A21-1)</f>
+        <v/>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr"/>
+      <c r="H21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="25">
+        <f>IF($E$3="","",$E$3+A22-1)</f>
+        <v/>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr"/>
+      <c r="H22" s="26" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="29">
+        <f>IF($E$3="","",$E$3+A23-1)</f>
+        <v/>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr"/>
+      <c r="H23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="29">
+        <f>IF($E$3="","",$E$3+A24-1)</f>
+        <v/>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr"/>
+      <c r="H24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="25">
+        <f>IF($E$3="","",$E$3+A25-1)</f>
+        <v/>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="inlineStr"/>
+      <c r="H25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="25">
+        <f>IF($E$3="","",$E$3+A26-1)</f>
+        <v/>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="inlineStr"/>
+      <c r="H26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="29">
+        <f>IF($E$3="","",$E$3+A27-1)</f>
+        <v/>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr"/>
+      <c r="H27" s="30" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="25">
+        <f>IF($E$3="","",$E$3+A28-1)</f>
+        <v/>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="inlineStr"/>
+      <c r="H28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="29">
+        <f>IF($E$3="","",$E$3+A29-1)</f>
+        <v/>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="inlineStr"/>
+      <c r="H29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B30" s="25">
+        <f>IF($E$3="","",$E$3+A30-1)</f>
+        <v/>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G30" s="27" t="inlineStr"/>
+      <c r="H30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B31" s="29">
+        <f>IF($E$3="","",$E$3+A31-1)</f>
+        <v/>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="inlineStr"/>
+      <c r="H31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B32" s="25">
+        <f>IF($E$3="","",$E$3+A32-1)</f>
+        <v/>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G32" s="27" t="inlineStr"/>
+      <c r="H32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="25">
+        <f>IF($E$3="","",$E$3+A33-1)</f>
+        <v/>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G33" s="27" t="inlineStr"/>
+      <c r="H33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="29">
+        <f>IF($E$3="","",$E$3+A34-1)</f>
+        <v/>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr"/>
+      <c r="H34" s="30" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" s="25">
+        <f>IF($E$3="","",$E$3+A35-1)</f>
+        <v/>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="inlineStr"/>
+      <c r="H35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="25">
+        <f>IF($E$3="","",$E$3+A36-1)</f>
+        <v/>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="G36" s="27" t="inlineStr"/>
+      <c r="H36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" s="25">
+        <f>IF($E$3="","",$E$3+A37-1)</f>
+        <v/>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="inlineStr"/>
+      <c r="H37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B38" s="25">
+        <f>IF($E$3="","",$E$3+A38-1)</f>
+        <v/>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr"/>
+      <c r="H38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="B39" s="29">
+        <f>IF($E$3="","",$E$3+A39-1)</f>
+        <v/>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="inlineStr"/>
+      <c r="H39" s="30" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" s="25">
+        <f>IF($E$3="","",$E$3+A40-1)</f>
+        <v/>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr"/>
+      <c r="H40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" s="25">
+        <f>IF($E$3="","",$E$3+A41-1)</f>
+        <v/>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="inlineStr"/>
+      <c r="H41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B42" s="25">
+        <f>IF($E$3="","",$E$3+A42-1)</f>
+        <v/>
+      </c>
+      <c r="C42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G42" s="27" t="inlineStr"/>
+      <c r="H42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B43" s="29">
+        <f>IF($E$3="","",$E$3+A43-1)</f>
+        <v/>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F43" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="inlineStr"/>
+      <c r="H43" s="30" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B44" s="25">
+        <f>IF($E$3="","",$E$3+A44-1)</f>
+        <v/>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G44" s="27" t="inlineStr"/>
+      <c r="H44" s="26" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" s="25">
+        <f>IF($E$3="","",$E$3+A45-1)</f>
+        <v/>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G45" s="27" t="inlineStr"/>
+      <c r="H45" s="26" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" s="25">
+        <f>IF($E$3="","",$E$3+A46-1)</f>
+        <v/>
+      </c>
+      <c r="C46" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G46" s="27" t="inlineStr"/>
+      <c r="H46" s="26" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B47" s="29">
+        <f>IF($E$3="","",$E$3+A47-1)</f>
+        <v/>
+      </c>
+      <c r="C47" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="31" t="inlineStr"/>
+      <c r="H47" s="30" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B48" s="25">
+        <f>IF($E$3="","",$E$3+A48-1)</f>
+        <v/>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G48" s="27" t="inlineStr"/>
+      <c r="H48" s="26" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B49" s="29">
+        <f>IF($E$3="","",$E$3+A49-1)</f>
+        <v/>
+      </c>
+      <c r="C49" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="31" t="inlineStr"/>
+      <c r="H49" s="30" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B50" s="29">
+        <f>IF($E$3="","",$E$3+A50-1)</f>
+        <v/>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="31" t="inlineStr"/>
+      <c r="H50" s="30" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B51" s="25">
+        <f>IF($E$3="","",$E$3+A51-1)</f>
+        <v/>
+      </c>
+      <c r="C51" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="G51" s="27" t="inlineStr"/>
+      <c r="H51" s="26" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B52" s="29">
+        <f>IF($E$3="","",$E$3+A52-1)</f>
+        <v/>
+      </c>
+      <c r="C52" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="31" t="inlineStr"/>
+      <c r="H52" s="30" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B53" s="29">
+        <f>IF($E$3="","",$E$3+A53-1)</f>
+        <v/>
+      </c>
+      <c r="C53" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="31" t="inlineStr"/>
+      <c r="H53" s="30" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B54" s="25">
+        <f>IF($E$3="","",$E$3+A54-1)</f>
+        <v/>
+      </c>
+      <c r="C54" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G54" s="27" t="inlineStr"/>
+      <c r="H54" s="26" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B55" s="25">
+        <f>IF($E$3="","",$E$3+A55-1)</f>
+        <v/>
+      </c>
+      <c r="C55" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G55" s="27" t="inlineStr"/>
+      <c r="H55" s="26" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B56" s="25">
+        <f>IF($E$3="","",$E$3+A56-1)</f>
+        <v/>
+      </c>
+      <c r="C56" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G56" s="27" t="inlineStr"/>
+      <c r="H56" s="26" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B57" s="25">
+        <f>IF($E$3="","",$E$3+A57-1)</f>
+        <v/>
+      </c>
+      <c r="C57" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G57" s="27" t="inlineStr"/>
+      <c r="H57" s="26" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B58" s="25">
+        <f>IF($E$3="","",$E$3+A58-1)</f>
+        <v/>
+      </c>
+      <c r="C58" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G58" s="27" t="inlineStr"/>
+      <c r="H58" s="26" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B59" s="25">
+        <f>IF($E$3="","",$E$3+A59-1)</f>
+        <v/>
+      </c>
+      <c r="C59" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G59" s="27" t="inlineStr"/>
+      <c r="H59" s="26" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B60" s="29">
+        <f>IF($E$3="","",$E$3+A60-1)</f>
+        <v/>
+      </c>
+      <c r="C60" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F60" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="31" t="inlineStr"/>
+      <c r="H60" s="30" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B61" s="25">
+        <f>IF($E$3="","",$E$3+A61-1)</f>
+        <v/>
+      </c>
+      <c r="C61" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G61" s="27" t="inlineStr"/>
+      <c r="H61" s="26" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B62" s="25">
+        <f>IF($E$3="","",$E$3+A62-1)</f>
+        <v/>
+      </c>
+      <c r="C62" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G62" s="27" t="inlineStr"/>
+      <c r="H62" s="26" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B63" s="25">
+        <f>IF($E$3="","",$E$3+A63-1)</f>
+        <v/>
+      </c>
+      <c r="C63" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G63" s="27" t="inlineStr"/>
+      <c r="H63" s="26" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B64" s="29">
+        <f>IF($E$3="","",$E$3+A64-1)</f>
+        <v/>
+      </c>
+      <c r="C64" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F64" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="31" t="inlineStr"/>
+      <c r="H64" s="30" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B65" s="25">
+        <f>IF($E$3="","",$E$3+A65-1)</f>
+        <v/>
+      </c>
+      <c r="C65" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G65" s="27" t="inlineStr"/>
+      <c r="H65" s="26" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B66" s="25">
+        <f>IF($E$3="","",$E$3+A66-1)</f>
+        <v/>
+      </c>
+      <c r="C66" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="G66" s="27" t="inlineStr"/>
+      <c r="H66" s="26" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B67" s="29">
+        <f>IF($E$3="","",$E$3+A67-1)</f>
+        <v/>
+      </c>
+      <c r="C67" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="31" t="inlineStr"/>
+      <c r="H67" s="30" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B68" s="25">
+        <f>IF($E$3="","",$E$3+A68-1)</f>
+        <v/>
+      </c>
+      <c r="C68" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G68" s="27" t="inlineStr"/>
+      <c r="H68" s="26" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B69" s="25">
+        <f>IF($E$3="","",$E$3+A69-1)</f>
+        <v/>
+      </c>
+      <c r="C69" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G69" s="27" t="inlineStr"/>
+      <c r="H69" s="26" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B70" s="29">
+        <f>IF($E$3="","",$E$3+A70-1)</f>
+        <v/>
+      </c>
+      <c r="C70" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E70" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F70" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr"/>
+      <c r="H70" s="30" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B71" s="25">
+        <f>IF($E$3="","",$E$3+A71-1)</f>
+        <v/>
+      </c>
+      <c r="C71" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G71" s="27" t="inlineStr"/>
+      <c r="H71" s="26" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B72" s="29">
+        <f>IF($E$3="","",$E$3+A72-1)</f>
+        <v/>
+      </c>
+      <c r="C72" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F72" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr"/>
+      <c r="H72" s="30" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B73" s="25">
+        <f>IF($E$3="","",$E$3+A73-1)</f>
+        <v/>
+      </c>
+      <c r="C73" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G73" s="27" t="inlineStr"/>
+      <c r="H73" s="26" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B74" s="25">
+        <f>IF($E$3="","",$E$3+A74-1)</f>
+        <v/>
+      </c>
+      <c r="C74" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G74" s="27" t="inlineStr"/>
+      <c r="H74" s="26" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B75" s="25">
+        <f>IF($E$3="","",$E$3+A75-1)</f>
+        <v/>
+      </c>
+      <c r="C75" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G75" s="27" t="inlineStr"/>
+      <c r="H75" s="26" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="B76" s="25">
+        <f>IF($E$3="","",$E$3+A76-1)</f>
+        <v/>
+      </c>
+      <c r="C76" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G76" s="27" t="inlineStr"/>
+      <c r="H76" s="26" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="B77" s="25">
+        <f>IF($E$3="","",$E$3+A77-1)</f>
+        <v/>
+      </c>
+      <c r="C77" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G77" s="27" t="inlineStr"/>
+      <c r="H77" s="26" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="B78" s="25">
+        <f>IF($E$3="","",$E$3+A78-1)</f>
+        <v/>
+      </c>
+      <c r="C78" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr"/>
+      <c r="H78" s="26" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B79" s="25">
+        <f>IF($E$3="","",$E$3+A79-1)</f>
+        <v/>
+      </c>
+      <c r="C79" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G79" s="27" t="inlineStr"/>
+      <c r="H79" s="26" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B80" s="25">
+        <f>IF($E$3="","",$E$3+A80-1)</f>
+        <v/>
+      </c>
+      <c r="C80" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr"/>
+      <c r="H80" s="26" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B81" s="29">
+        <f>IF($E$3="","",$E$3+A81-1)</f>
+        <v/>
+      </c>
+      <c r="C81" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F81" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr"/>
+      <c r="H81" s="30" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B82" s="25">
+        <f>IF($E$3="","",$E$3+A82-1)</f>
+        <v/>
+      </c>
+      <c r="C82" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr"/>
+      <c r="H82" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B83" s="25">
+        <f>IF($E$3="","",$E$3+A83-1)</f>
+        <v/>
+      </c>
+      <c r="C83" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G83" s="27" t="inlineStr"/>
+      <c r="H83" s="26" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B84" s="25">
+        <f>IF($E$3="","",$E$3+A84-1)</f>
+        <v/>
+      </c>
+      <c r="C84" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr"/>
+      <c r="H84" s="26" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="B85" s="25">
+        <f>IF($E$3="","",$E$3+A85-1)</f>
+        <v/>
+      </c>
+      <c r="C85" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G85" s="27" t="inlineStr"/>
+      <c r="H85" s="26" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B86" s="29">
+        <f>IF($E$3="","",$E$3+A86-1)</f>
+        <v/>
+      </c>
+      <c r="C86" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F86" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="31" t="inlineStr"/>
+      <c r="H86" s="30" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B87" s="29">
+        <f>IF($E$3="","",$E$3+A87-1)</f>
+        <v/>
+      </c>
+      <c r="C87" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E87" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F87" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="31" t="inlineStr"/>
+      <c r="H87" s="30" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B88" s="25">
+        <f>IF($E$3="","",$E$3+A88-1)</f>
+        <v/>
+      </c>
+      <c r="C88" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr"/>
+      <c r="H88" s="26" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B89" s="25">
+        <f>IF($E$3="","",$E$3+A89-1)</f>
+        <v/>
+      </c>
+      <c r="C89" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G89" s="27" t="inlineStr"/>
+      <c r="H89" s="26" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B90" s="25">
+        <f>IF($E$3="","",$E$3+A90-1)</f>
+        <v/>
+      </c>
+      <c r="C90" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr"/>
+      <c r="H90" s="26" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="B91" s="25">
+        <f>IF($E$3="","",$E$3+A91-1)</f>
+        <v/>
+      </c>
+      <c r="C91" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G91" s="27" t="inlineStr"/>
+      <c r="H91" s="26" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B92" s="29">
+        <f>IF($E$3="","",$E$3+A92-1)</f>
+        <v/>
+      </c>
+      <c r="C92" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F92" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="31" t="inlineStr"/>
+      <c r="H92" s="30" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B93" s="29">
+        <f>IF($E$3="","",$E$3+A93-1)</f>
+        <v/>
+      </c>
+      <c r="C93" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F93" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="31" t="inlineStr"/>
+      <c r="H93" s="30" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="B94" s="25">
+        <f>IF($E$3="","",$E$3+A94-1)</f>
+        <v/>
+      </c>
+      <c r="C94" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F94" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G94" s="27" t="inlineStr"/>
+      <c r="H94" s="26" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="B95" s="25">
+        <f>IF($E$3="","",$E$3+A95-1)</f>
+        <v/>
+      </c>
+      <c r="C95" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G95" s="27" t="inlineStr"/>
+      <c r="H95" s="26" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="B96" s="25">
+        <f>IF($E$3="","",$E$3+A96-1)</f>
+        <v/>
+      </c>
+      <c r="C96" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F96" s="24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="G96" s="27" t="inlineStr"/>
+      <c r="H96" s="26" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="B97" s="25">
+        <f>IF($E$3="","",$E$3+A97-1)</f>
+        <v/>
+      </c>
+      <c r="C97" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F97" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G97" s="27" t="inlineStr"/>
+      <c r="H97" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B98" s="29">
+        <f>IF($E$3="","",$E$3+A98-1)</f>
+        <v/>
+      </c>
+      <c r="C98" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E98" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F98" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="31" t="inlineStr"/>
+      <c r="H98" s="30" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="B99" s="25">
+        <f>IF($E$3="","",$E$3+A99-1)</f>
+        <v/>
+      </c>
+      <c r="C99" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E99" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F99" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G99" s="27" t="inlineStr"/>
+      <c r="H99" s="26" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="B100" s="25">
+        <f>IF($E$3="","",$E$3+A100-1)</f>
+        <v/>
+      </c>
+      <c r="C100" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E100" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F100" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G100" s="27" t="inlineStr"/>
+      <c r="H100" s="26" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="24" t="n">
+        <v>37</v>
+      </c>
+      <c r="B101" s="25">
+        <f>IF($E$3="","",$E$3+A101-1)</f>
+        <v/>
+      </c>
+      <c r="C101" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F101" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G101" s="27" t="inlineStr"/>
+      <c r="H101" s="26" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B102" s="29">
+        <f>IF($E$3="","",$E$3+A102-1)</f>
+        <v/>
+      </c>
+      <c r="C102" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F102" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="31" t="inlineStr"/>
+      <c r="H102" s="30" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="24" t="n">
+        <v>37</v>
+      </c>
+      <c r="B103" s="25">
+        <f>IF($E$3="","",$E$3+A103-1)</f>
+        <v/>
+      </c>
+      <c r="C103" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E103" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F103" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G103" s="27" t="inlineStr"/>
+      <c r="H103" s="26" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="24" t="n">
+        <v>37</v>
+      </c>
+      <c r="B104" s="25">
+        <f>IF($E$3="","",$E$3+A104-1)</f>
+        <v/>
+      </c>
+      <c r="C104" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G104" s="27" t="inlineStr"/>
+      <c r="H104" s="26" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B105" s="25">
+        <f>IF($E$3="","",$E$3+A105-1)</f>
+        <v/>
+      </c>
+      <c r="C105" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G105" s="27" t="inlineStr"/>
+      <c r="H105" s="26" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="B106" s="29">
+        <f>IF($E$3="","",$E$3+A106-1)</f>
+        <v/>
+      </c>
+      <c r="C106" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E106" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F106" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="31" t="inlineStr"/>
+      <c r="H106" s="30" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B107" s="25">
+        <f>IF($E$3="","",$E$3+A107-1)</f>
+        <v/>
+      </c>
+      <c r="C107" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G107" s="27" t="inlineStr"/>
+      <c r="H107" s="26" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B108" s="25">
+        <f>IF($E$3="","",$E$3+A108-1)</f>
+        <v/>
+      </c>
+      <c r="C108" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E108" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G108" s="27" t="inlineStr"/>
+      <c r="H108" s="26" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="B109" s="29">
+        <f>IF($E$3="","",$E$3+A109-1)</f>
+        <v/>
+      </c>
+      <c r="C109" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F109" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="31" t="inlineStr"/>
+      <c r="H109" s="30" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="24" t="n">
+        <v>39</v>
+      </c>
+      <c r="B110" s="25">
+        <f>IF($E$3="","",$E$3+A110-1)</f>
+        <v/>
+      </c>
+      <c r="C110" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G110" s="27" t="inlineStr"/>
+      <c r="H110" s="26" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="24" t="n">
+        <v>39</v>
+      </c>
+      <c r="B111" s="25">
+        <f>IF($E$3="","",$E$3+A111-1)</f>
+        <v/>
+      </c>
+      <c r="C111" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G111" s="27" t="inlineStr"/>
+      <c r="H111" s="26" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="24" t="n">
+        <v>39</v>
+      </c>
+      <c r="B112" s="25">
+        <f>IF($E$3="","",$E$3+A112-1)</f>
+        <v/>
+      </c>
+      <c r="C112" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" s="26" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G112" s="27" t="inlineStr"/>
+      <c r="H112" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="B113" s="25">
+        <f>IF($E$3="","",$E$3+A113-1)</f>
+        <v/>
+      </c>
+      <c r="C113" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G113" s="27" t="inlineStr"/>
+      <c r="H113" s="26" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="B114" s="25">
+        <f>IF($E$3="","",$E$3+A114-1)</f>
+        <v/>
+      </c>
+      <c r="C114" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G114" s="27" t="inlineStr"/>
+      <c r="H114" s="26" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="B115" s="29">
+        <f>IF($E$3="","",$E$3+A115-1)</f>
+        <v/>
+      </c>
+      <c r="C115" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F115" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="31" t="inlineStr"/>
+      <c r="H115" s="30" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="B116" s="25">
+        <f>IF($E$3="","",$E$3+A116-1)</f>
+        <v/>
+      </c>
+      <c r="C116" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G116" s="27" t="inlineStr"/>
+      <c r="H116" s="26" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="B117" s="25">
+        <f>IF($E$3="","",$E$3+A117-1)</f>
+        <v/>
+      </c>
+      <c r="C117" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G117" s="27" t="inlineStr"/>
+      <c r="H117" s="26" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="28" t="n">
+        <v>41</v>
+      </c>
+      <c r="B118" s="29">
+        <f>IF($E$3="","",$E$3+A118-1)</f>
+        <v/>
+      </c>
+      <c r="C118" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F118" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="31" t="inlineStr"/>
+      <c r="H118" s="30" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="B119" s="25">
+        <f>IF($E$3="","",$E$3+A119-1)</f>
+        <v/>
+      </c>
+      <c r="C119" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G119" s="27" t="inlineStr"/>
+      <c r="H119" s="26" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="B120" s="25">
+        <f>IF($E$3="","",$E$3+A120-1)</f>
+        <v/>
+      </c>
+      <c r="C120" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G120" s="27" t="inlineStr"/>
+      <c r="H120" s="26" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="B121" s="29">
+        <f>IF($E$3="","",$E$3+A121-1)</f>
+        <v/>
+      </c>
+      <c r="C121" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E121" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F121" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="31" t="inlineStr"/>
+      <c r="H121" s="30" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="B122" s="29">
+        <f>IF($E$3="","",$E$3+A122-1)</f>
+        <v/>
+      </c>
+      <c r="C122" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F122" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="31" t="inlineStr"/>
+      <c r="H122" s="30" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="24" t="n">
+        <v>42</v>
+      </c>
+      <c r="B123" s="25">
+        <f>IF($E$3="","",$E$3+A123-1)</f>
+        <v/>
+      </c>
+      <c r="C123" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E123" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F123" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G123" s="27" t="inlineStr"/>
+      <c r="H123" s="26" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="24" t="n">
+        <v>42</v>
+      </c>
+      <c r="B124" s="25">
+        <f>IF($E$3="","",$E$3+A124-1)</f>
+        <v/>
+      </c>
+      <c r="C124" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E124" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F124" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G124" s="27" t="inlineStr"/>
+      <c r="H124" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="B125" s="29">
+        <f>IF($E$3="","",$E$3+A125-1)</f>
+        <v/>
+      </c>
+      <c r="C125" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F125" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G125" s="31" t="inlineStr"/>
+      <c r="H125" s="30" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="B126" s="25">
+        <f>IF($E$3="","",$E$3+A126-1)</f>
+        <v/>
+      </c>
+      <c r="C126" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E126" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F126" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G126" s="27" t="inlineStr"/>
+      <c r="H126" s="26" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="B127" s="25">
+        <f>IF($E$3="","",$E$3+A127-1)</f>
+        <v/>
+      </c>
+      <c r="C127" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E127" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G127" s="27" t="inlineStr"/>
+      <c r="H127" s="26" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="B128" s="29">
+        <f>IF($E$3="","",$E$3+A128-1)</f>
+        <v/>
+      </c>
+      <c r="C128" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F128" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="31" t="inlineStr"/>
+      <c r="H128" s="30" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="B129" s="25">
+        <f>IF($E$3="","",$E$3+A129-1)</f>
+        <v/>
+      </c>
+      <c r="C129" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E129" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F129" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G129" s="27" t="inlineStr"/>
+      <c r="H129" s="26" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="B130" s="25">
+        <f>IF($E$3="","",$E$3+A130-1)</f>
+        <v/>
+      </c>
+      <c r="C130" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E130" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F130" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G130" s="27" t="inlineStr"/>
+      <c r="H130" s="26" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="B131" s="25">
+        <f>IF($E$3="","",$E$3+A131-1)</f>
+        <v/>
+      </c>
+      <c r="C131" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D131" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E131" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F131" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G131" s="27" t="inlineStr"/>
+      <c r="H131" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="B132" s="25">
+        <f>IF($E$3="","",$E$3+A132-1)</f>
+        <v/>
+      </c>
+      <c r="C132" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D132" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E132" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F132" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G132" s="27" t="inlineStr"/>
+      <c r="H132" s="26" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B133" s="25">
+        <f>IF($E$3="","",$E$3+A133-1)</f>
+        <v/>
+      </c>
+      <c r="C133" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E133" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F133" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G133" s="27" t="inlineStr"/>
+      <c r="H133" s="26" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B134" s="25">
+        <f>IF($E$3="","",$E$3+A134-1)</f>
+        <v/>
+      </c>
+      <c r="C134" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E134" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G134" s="27" t="inlineStr"/>
+      <c r="H134" s="26" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B135" s="25">
+        <f>IF($E$3="","",$E$3+A135-1)</f>
+        <v/>
+      </c>
+      <c r="C135" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D135" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E135" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F135" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G135" s="27" t="inlineStr"/>
+      <c r="H135" s="26" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B136" s="25">
+        <f>IF($E$3="","",$E$3+A136-1)</f>
+        <v/>
+      </c>
+      <c r="C136" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D136" s="26" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="E136" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F136" s="24" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G136" s="27" t="inlineStr"/>
+      <c r="H136" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="24" t="n">
+        <v>46</v>
+      </c>
+      <c r="B137" s="25">
+        <f>IF($E$3="","",$E$3+A137-1)</f>
+        <v/>
+      </c>
+      <c r="C137" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E137" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G137" s="27" t="inlineStr"/>
+      <c r="H137" s="26" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="24" t="n">
+        <v>46</v>
+      </c>
+      <c r="B138" s="25">
+        <f>IF($E$3="","",$E$3+A138-1)</f>
+        <v/>
+      </c>
+      <c r="C138" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E138" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G138" s="27" t="inlineStr"/>
+      <c r="H138" s="26" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="24" t="n">
+        <v>46</v>
+      </c>
+      <c r="B139" s="25">
+        <f>IF($E$3="","",$E$3+A139-1)</f>
+        <v/>
+      </c>
+      <c r="C139" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" s="26" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="E139" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G139" s="27" t="inlineStr"/>
+      <c r="H139" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="24" t="n">
+        <v>46</v>
+      </c>
+      <c r="B140" s="25">
+        <f>IF($E$3="","",$E$3+A140-1)</f>
+        <v/>
+      </c>
+      <c r="C140" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E140" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F140" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G140" s="27" t="inlineStr"/>
+      <c r="H140" s="26" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="28" t="n">
+        <v>47</v>
+      </c>
+      <c r="B141" s="29">
+        <f>IF($E$3="","",$E$3+A141-1)</f>
+        <v/>
+      </c>
+      <c r="C141" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E141" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F141" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" s="31" t="inlineStr"/>
+      <c r="H141" s="30" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="24" t="n">
+        <v>47</v>
+      </c>
+      <c r="B142" s="25">
+        <f>IF($E$3="","",$E$3+A142-1)</f>
+        <v/>
+      </c>
+      <c r="C142" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E142" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F142" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G142" s="27" t="inlineStr"/>
+      <c r="H142" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="28" t="n">
+        <v>47</v>
+      </c>
+      <c r="B143" s="29">
+        <f>IF($E$3="","",$E$3+A143-1)</f>
+        <v/>
+      </c>
+      <c r="C143" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D143" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E143" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F143" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G143" s="31" t="inlineStr"/>
+      <c r="H143" s="30" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="24" t="n">
+        <v>47</v>
+      </c>
+      <c r="B144" s="25">
+        <f>IF($E$3="","",$E$3+A144-1)</f>
+        <v/>
+      </c>
+      <c r="C144" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D144" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E144" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F144" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G144" s="27" t="inlineStr"/>
+      <c r="H144" s="26" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="B145" s="29">
+        <f>IF($E$3="","",$E$3+A145-1)</f>
+        <v/>
+      </c>
+      <c r="C145" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E145" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F145" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="31" t="inlineStr"/>
+      <c r="H145" s="30" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="B146" s="25">
+        <f>IF($E$3="","",$E$3+A146-1)</f>
+        <v/>
+      </c>
+      <c r="C146" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E146" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F146" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G146" s="27" t="inlineStr"/>
+      <c r="H146" s="26" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="B147" s="25">
+        <f>IF($E$3="","",$E$3+A147-1)</f>
+        <v/>
+      </c>
+      <c r="C147" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E147" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G147" s="27" t="inlineStr"/>
+      <c r="H147" s="26" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="B148" s="25">
+        <f>IF($E$3="","",$E$3+A148-1)</f>
+        <v/>
+      </c>
+      <c r="C148" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D148" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E148" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F148" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G148" s="27" t="inlineStr"/>
+      <c r="H148" s="26" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="24" t="n">
+        <v>49</v>
+      </c>
+      <c r="B149" s="25">
+        <f>IF($E$3="","",$E$3+A149-1)</f>
+        <v/>
+      </c>
+      <c r="C149" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E149" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F149" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G149" s="27" t="inlineStr"/>
+      <c r="H149" s="26" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="28" t="n">
+        <v>49</v>
+      </c>
+      <c r="B150" s="29">
+        <f>IF($E$3="","",$E$3+A150-1)</f>
+        <v/>
+      </c>
+      <c r="C150" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E150" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F150" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="31" t="inlineStr"/>
+      <c r="H150" s="30" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="28" t="n">
+        <v>49</v>
+      </c>
+      <c r="B151" s="29">
+        <f>IF($E$3="","",$E$3+A151-1)</f>
+        <v/>
+      </c>
+      <c r="C151" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E151" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F151" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="31" t="inlineStr"/>
+      <c r="H151" s="30" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="24" t="n">
+        <v>49</v>
+      </c>
+      <c r="B152" s="25">
+        <f>IF($E$3="","",$E$3+A152-1)</f>
+        <v/>
+      </c>
+      <c r="C152" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D152" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E152" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F152" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G152" s="27" t="inlineStr"/>
+      <c r="H152" s="26" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="B153" s="29">
+        <f>IF($E$3="","",$E$3+A153-1)</f>
+        <v/>
+      </c>
+      <c r="C153" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E153" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F153" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G153" s="31" t="inlineStr"/>
+      <c r="H153" s="30" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="B154" s="25">
+        <f>IF($E$3="","",$E$3+A154-1)</f>
+        <v/>
+      </c>
+      <c r="C154" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E154" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F154" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G154" s="27" t="inlineStr"/>
+      <c r="H154" s="26" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="B155" s="25">
+        <f>IF($E$3="","",$E$3+A155-1)</f>
+        <v/>
+      </c>
+      <c r="C155" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D155" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E155" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F155" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G155" s="27" t="inlineStr"/>
+      <c r="H155" s="26" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="B156" s="25">
+        <f>IF($E$3="","",$E$3+A156-1)</f>
+        <v/>
+      </c>
+      <c r="C156" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D156" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E156" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F156" s="24" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G156" s="27" t="inlineStr"/>
+      <c r="H156" s="26" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="24" t="n">
+        <v>51</v>
+      </c>
+      <c r="B157" s="25">
+        <f>IF($E$3="","",$E$3+A157-1)</f>
+        <v/>
+      </c>
+      <c r="C157" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E157" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F157" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G157" s="27" t="inlineStr"/>
+      <c r="H157" s="26" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="24" t="n">
+        <v>51</v>
+      </c>
+      <c r="B158" s="25">
+        <f>IF($E$3="","",$E$3+A158-1)</f>
+        <v/>
+      </c>
+      <c r="C158" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E158" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F158" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G158" s="27" t="inlineStr"/>
+      <c r="H158" s="26" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="28" t="n">
+        <v>51</v>
+      </c>
+      <c r="B159" s="29">
+        <f>IF($E$3="","",$E$3+A159-1)</f>
+        <v/>
+      </c>
+      <c r="C159" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E159" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F159" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G159" s="31" t="inlineStr"/>
+      <c r="H159" s="30" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="24" t="n">
+        <v>51</v>
+      </c>
+      <c r="B160" s="25">
+        <f>IF($E$3="","",$E$3+A160-1)</f>
+        <v/>
+      </c>
+      <c r="C160" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E160" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F160" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G160" s="27" t="inlineStr"/>
+      <c r="H160" s="26" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="B161" s="29">
+        <f>IF($E$3="","",$E$3+A161-1)</f>
+        <v/>
+      </c>
+      <c r="C161" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E161" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F161" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G161" s="31" t="inlineStr"/>
+      <c r="H161" s="30" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="B162" s="29">
+        <f>IF($E$3="","",$E$3+A162-1)</f>
+        <v/>
+      </c>
+      <c r="C162" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E162" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F162" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G162" s="31" t="inlineStr"/>
+      <c r="H162" s="30" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="24" t="n">
+        <v>52</v>
+      </c>
+      <c r="B163" s="25">
+        <f>IF($E$3="","",$E$3+A163-1)</f>
+        <v/>
+      </c>
+      <c r="C163" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D163" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E163" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F163" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G163" s="27" t="inlineStr"/>
+      <c r="H163" s="26" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="24" t="n">
+        <v>52</v>
+      </c>
+      <c r="B164" s="25">
+        <f>IF($E$3="","",$E$3+A164-1)</f>
+        <v/>
+      </c>
+      <c r="C164" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D164" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E164" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F164" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G164" s="27" t="inlineStr"/>
+      <c r="H164" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="28" t="n">
+        <v>53</v>
+      </c>
+      <c r="B165" s="29">
+        <f>IF($E$3="","",$E$3+A165-1)</f>
+        <v/>
+      </c>
+      <c r="C165" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E165" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F165" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G165" s="31" t="inlineStr"/>
+      <c r="H165" s="30" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="B166" s="25">
+        <f>IF($E$3="","",$E$3+A166-1)</f>
+        <v/>
+      </c>
+      <c r="C166" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" s="26" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="E166" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F166" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G166" s="27" t="inlineStr"/>
+      <c r="H166" s="26" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="28" t="n">
+        <v>53</v>
+      </c>
+      <c r="B167" s="29">
+        <f>IF($E$3="","",$E$3+A167-1)</f>
+        <v/>
+      </c>
+      <c r="C167" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D167" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E167" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F167" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G167" s="31" t="inlineStr"/>
+      <c r="H167" s="30" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="B168" s="25">
+        <f>IF($E$3="","",$E$3+A168-1)</f>
+        <v/>
+      </c>
+      <c r="C168" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D168" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E168" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F168" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G168" s="27" t="inlineStr"/>
+      <c r="H168" s="26" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="B169" s="29">
+        <f>IF($E$3="","",$E$3+A169-1)</f>
+        <v/>
+      </c>
+      <c r="C169" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" s="30" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="E169" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F169" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G169" s="31" t="inlineStr"/>
+      <c r="H169" s="30" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="B170" s="25">
+        <f>IF($E$3="","",$E$3+A170-1)</f>
+        <v/>
+      </c>
+      <c r="C170" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E170" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F170" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G170" s="27" t="inlineStr"/>
+      <c r="H170" s="26" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="B171" s="25">
+        <f>IF($E$3="","",$E$3+A171-1)</f>
+        <v/>
+      </c>
+      <c r="C171" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D171" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E171" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F171" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G171" s="27" t="inlineStr"/>
+      <c r="H171" s="26" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="B172" s="25">
+        <f>IF($E$3="","",$E$3+A172-1)</f>
+        <v/>
+      </c>
+      <c r="C172" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D172" s="26" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="E172" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F172" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G172" s="27" t="inlineStr"/>
+      <c r="H172" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="B173" s="25">
+        <f>IF($E$3="","",$E$3+A173-1)</f>
+        <v/>
+      </c>
+      <c r="C173" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="26" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="E173" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F173" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G173" s="27" t="inlineStr"/>
+      <c r="H173" s="26" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="B174" s="29">
+        <f>IF($E$3="","",$E$3+A174-1)</f>
+        <v/>
+      </c>
+      <c r="C174" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E174" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F174" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="31" t="inlineStr"/>
+      <c r="H174" s="30" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="B175" s="25">
+        <f>IF($E$3="","",$E$3+A175-1)</f>
+        <v/>
+      </c>
+      <c r="C175" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E175" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F175" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G175" s="27" t="inlineStr"/>
+      <c r="H175" s="26" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="B176" s="25">
+        <f>IF($E$3="","",$E$3+A176-1)</f>
+        <v/>
+      </c>
+      <c r="C176" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D176" s="26" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="E176" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F176" s="24" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G176" s="27" t="inlineStr"/>
+      <c r="H176" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="24" t="n">
+        <v>56</v>
+      </c>
+      <c r="B177" s="25">
+        <f>IF($E$3="","",$E$3+A177-1)</f>
+        <v/>
+      </c>
+      <c r="C177" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E177" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F177" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G177" s="27" t="inlineStr"/>
+      <c r="H177" s="26" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="24" t="n">
+        <v>56</v>
+      </c>
+      <c r="B178" s="25">
+        <f>IF($E$3="","",$E$3+A178-1)</f>
+        <v/>
+      </c>
+      <c r="C178" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E178" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F178" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G178" s="27" t="inlineStr"/>
+      <c r="H178" s="26" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="24" t="n">
+        <v>56</v>
+      </c>
+      <c r="B179" s="25">
+        <f>IF($E$3="","",$E$3+A179-1)</f>
+        <v/>
+      </c>
+      <c r="C179" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E179" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F179" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G179" s="27" t="inlineStr"/>
+      <c r="H179" s="26" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="24" t="n">
+        <v>56</v>
+      </c>
+      <c r="B180" s="25">
+        <f>IF($E$3="","",$E$3+A180-1)</f>
+        <v/>
+      </c>
+      <c r="C180" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D180" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E180" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F180" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G180" s="27" t="inlineStr"/>
+      <c r="H180" s="26" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="B181" s="29">
+        <f>IF($E$3="","",$E$3+A181-1)</f>
+        <v/>
+      </c>
+      <c r="C181" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" s="30" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="E181" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="F181" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G181" s="31" t="inlineStr"/>
+      <c r="H181" s="30" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="24" t="n">
+        <v>57</v>
+      </c>
+      <c r="B182" s="25">
+        <f>IF($E$3="","",$E$3+A182-1)</f>
+        <v/>
+      </c>
+      <c r="C182" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E182" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F182" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G182" s="27" t="inlineStr"/>
+      <c r="H182" s="26" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="24" t="n">
+        <v>57</v>
+      </c>
+      <c r="B183" s="25">
+        <f>IF($E$3="","",$E$3+A183-1)</f>
+        <v/>
+      </c>
+      <c r="C183" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D183" s="26" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="E183" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F183" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G183" s="27" t="inlineStr"/>
+      <c r="H183" s="26" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="24" t="n">
+        <v>57</v>
+      </c>
+      <c r="B184" s="25">
+        <f>IF($E$3="","",$E$3+A184-1)</f>
+        <v/>
+      </c>
+      <c r="C184" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D184" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E184" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F184" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G184" s="27" t="inlineStr"/>
+      <c r="H184" s="26" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="B185" s="25">
+        <f>IF($E$3="","",$E$3+A185-1)</f>
+        <v/>
+      </c>
+      <c r="C185" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E185" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F185" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G185" s="27" t="inlineStr"/>
+      <c r="H185" s="26" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="B186" s="25">
+        <f>IF($E$3="","",$E$3+A186-1)</f>
+        <v/>
+      </c>
+      <c r="C186" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" s="26" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="E186" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F186" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G186" s="27" t="inlineStr"/>
+      <c r="H186" s="26" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="B187" s="25">
+        <f>IF($E$3="","",$E$3+A187-1)</f>
+        <v/>
+      </c>
+      <c r="C187" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E187" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F187" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G187" s="27" t="inlineStr"/>
+      <c r="H187" s="26" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="B188" s="25">
+        <f>IF($E$3="","",$E$3+A188-1)</f>
+        <v/>
+      </c>
+      <c r="C188" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D188" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E188" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F188" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G188" s="27" t="inlineStr"/>
+      <c r="H188" s="26" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="B189" s="25">
+        <f>IF($E$3="","",$E$3+A189-1)</f>
+        <v/>
+      </c>
+      <c r="C189" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E189" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F189" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G189" s="27" t="inlineStr"/>
+      <c r="H189" s="26" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="B190" s="25">
+        <f>IF($E$3="","",$E$3+A190-1)</f>
+        <v/>
+      </c>
+      <c r="C190" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E190" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F190" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G190" s="27" t="inlineStr"/>
+      <c r="H190" s="26" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="B191" s="25">
+        <f>IF($E$3="","",$E$3+A191-1)</f>
+        <v/>
+      </c>
+      <c r="C191" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E191" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F191" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G191" s="27" t="inlineStr"/>
+      <c r="H191" s="26" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="B192" s="25">
+        <f>IF($E$3="","",$E$3+A192-1)</f>
+        <v/>
+      </c>
+      <c r="C192" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D192" s="26" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="E192" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F192" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G192" s="27" t="inlineStr"/>
+      <c r="H192" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — publish when it happens, never force it</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="B193" s="25">
+        <f>IF($E$3="","",$E$3+A193-1)</f>
+        <v/>
+      </c>
+      <c r="C193" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" s="26" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="E193" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F193" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G193" s="27" t="inlineStr"/>
+      <c r="H193" s="26" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="B194" s="25">
+        <f>IF($E$3="","",$E$3+A194-1)</f>
+        <v/>
+      </c>
+      <c r="C194" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" s="26" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="E194" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F194" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G194" s="27" t="inlineStr"/>
+      <c r="H194" s="26" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="B195" s="25">
+        <f>IF($E$3="","",$E$3+A195-1)</f>
+        <v/>
+      </c>
+      <c r="C195" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" s="26" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="E195" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F195" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G195" s="27" t="inlineStr"/>
+      <c r="H195" s="26" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="B196" s="25">
+        <f>IF($E$3="","",$E$3+A196-1)</f>
+        <v/>
+      </c>
+      <c r="C196" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D196" s="26" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="E196" s="24" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F196" s="24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G196" s="27" t="inlineStr"/>
+      <c r="H196" s="26" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>COVERAGE CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>Meets 5-sample minimum?</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="B201" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C201" s="18">
+        <f>IF(B201&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="B202" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C202" s="18">
+        <f>IF(B202&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="B203" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C203" s="18">
+        <f>IF(B203&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="B204" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="C204" s="18">
+        <f>IF(B204&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="B205" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C205" s="18">
+        <f>IF(B205&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="18" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="B206" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C206" s="18">
+        <f>IF(B206&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="18" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="B207" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C207" s="18">
+        <f>IF(B207&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="18" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="B208" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="C208" s="18">
+        <f>IF(B208&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="18" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="B209" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C209" s="18">
+        <f>IF(B209&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="18" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="B210" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="C210" s="18">
+        <f>IF(B210&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="18" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="B211" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C211" s="18">
+        <f>IF(B211&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="18" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="B212" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C212" s="18">
+        <f>IF(B212&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Total pieces</t>
+        </is>
+      </c>
+      <c r="B214" s="33">
+        <f>SUM(B201:B213)</f>
+        <v/>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>x4 platforms = total uploads</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Field shoot days needed</t>
+        </is>
+      </c>
+      <c r="B215" s="33">
+        <f>ROUNDUP(COUNTIF(E6:E196,"Field")/10,0)</f>
+        <v/>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Assumes ~10 usable pieces per field day — adjust once you know your real yield.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13317,7 +19260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13846,7 +19789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/tools/format-rd-tracker.xlsx
+++ b/tools/format-rd-tracker.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="60-Day Plan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Post Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Format Scorecard" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Seeding Tracker" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hook Bank" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Post Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Format Scorecard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Seeding Tracker" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,10 +25,10 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="ddd dd mmm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="ddd dd mmm yyyy"/>
+    <numFmt numFmtId="167" formatCode="ddd dd mmm yyyy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +90,11 @@
       <b val="1"/>
       <sz val="15"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A1814"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -149,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,7 +218,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -814,17 +829,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,18 +853,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>191 original pieces in 60 days. Each one cross-posts to Instagram Reels, TikTok, YouTube Shorts and Facebook Reels — 4x the reach for no extra filming.</t>
+          <t>191 original pieces in 60 days, each with a hook ready to shoot. Every piece cross-posts to Instagram Reels, TikTok, YouTube Shorts and Facebook Reels.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Start date (edit this — every date below follows from it):</t>
-        </is>
-      </c>
-      <c r="E3" s="34" t="n">
+          <t>Start date:</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="n">
         <v>46244</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Edit the yellow cell — all 191 dates follow from it.</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -874,20 +895,25 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
+          <t>Hook to use</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Shoot batch</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Posted?</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -898,7 +924,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="25">
-        <f>IF($E$3="","",$E$3+A6-1)</f>
+        <f>IF($B$3="","",$B$3+A6-1)</f>
         <v/>
       </c>
       <c r="C6" s="24" t="n">
@@ -909,25 +935,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>That tone means it's silver.</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="G6" s="27" t="inlineStr"/>
-      <c r="H6" s="26" t="n"/>
+      <c r="H6" s="27" t="inlineStr"/>
+      <c r="I6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="29">
-        <f>IF($E$3="","",$E$3+A7-1)</f>
+        <f>IF($B$3="","",$B$3+A7-1)</f>
         <v/>
       </c>
       <c r="C7" s="28" t="n">
@@ -938,25 +969,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>He has no idea what he just dug up.</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr"/>
-      <c r="H7" s="30" t="n"/>
+      <c r="H7" s="31" t="inlineStr"/>
+      <c r="I7" s="30" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="24" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="25">
-        <f>IF($E$3="","",$E$3+A8-1)</f>
+        <f>IF($B$3="","",$B$3+A8-1)</f>
         <v/>
       </c>
       <c r="C8" s="24" t="n">
@@ -967,25 +1003,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>I almost walked past this.</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr"/>
-      <c r="H8" s="26" t="n"/>
+      <c r="H8" s="27" t="inlineStr"/>
+      <c r="I8" s="26" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="24" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="25">
-        <f>IF($E$3="","",$E$3+A9-1)</f>
+        <f>IF($B$3="","",$B$3+A9-1)</f>
         <v/>
       </c>
       <c r="C9" s="24" t="n">
@@ -996,25 +1037,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>This $300 detector says there's nothing here.</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="G9" s="27" t="inlineStr"/>
-      <c r="H9" s="26" t="n"/>
+      <c r="H9" s="27" t="inlineStr"/>
+      <c r="I9" s="26" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="24" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="25">
-        <f>IF($E$3="","",$E$3+A10-1)</f>
+        <f>IF($B$3="","",$B$3+A10-1)</f>
         <v/>
       </c>
       <c r="C10" s="24" t="n">
@@ -1025,25 +1071,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>Two inches down and it's already shining.</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="G10" s="27" t="inlineStr"/>
-      <c r="H10" s="26" t="n"/>
+      <c r="H10" s="27" t="inlineStr"/>
+      <c r="I10" s="26" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="29">
-        <f>IF($E$3="","",$E$3+A11-1)</f>
+        <f>IF($B$3="","",$B$3+A11-1)</f>
         <v/>
       </c>
       <c r="C11" s="28" t="n">
@@ -1054,25 +1105,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Sixty years of dirt. Watch.</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr"/>
-      <c r="H11" s="30" t="n"/>
+      <c r="H11" s="31" t="inlineStr"/>
+      <c r="I11" s="30" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="24" t="n">
         <v>4</v>
       </c>
       <c r="B12" s="25">
-        <f>IF($E$3="","",$E$3+A12-1)</f>
+        <f>IF($B$3="","",$B$3+A12-1)</f>
         <v/>
       </c>
       <c r="C12" s="24" t="n">
@@ -1083,25 +1139,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>That's not a bottle cap.</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr"/>
-      <c r="H12" s="26" t="n"/>
+      <c r="H12" s="27" t="inlineStr"/>
+      <c r="I12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B13" s="29">
-        <f>IF($E$3="","",$E$3+A13-1)</f>
+        <f>IF($B$3="","",$B$3+A13-1)</f>
         <v/>
       </c>
       <c r="C13" s="28" t="n">
@@ -1112,25 +1173,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>You will not believe what's under this.</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr"/>
-      <c r="H13" s="30" t="n"/>
+      <c r="H13" s="31" t="inlineStr"/>
+      <c r="I13" s="30" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="n">
         <v>5</v>
       </c>
       <c r="B14" s="25">
-        <f>IF($E$3="","",$E$3+A14-1)</f>
+        <f>IF($B$3="","",$B$3+A14-1)</f>
         <v/>
       </c>
       <c r="C14" s="24" t="n">
@@ -1141,25 +1207,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>Most people walk away from this sound. Don't.</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr"/>
-      <c r="H14" s="26" t="n"/>
+      <c r="H14" s="27" t="inlineStr"/>
+      <c r="I14" s="26" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="28" t="n">
         <v>5</v>
       </c>
       <c r="B15" s="29">
-        <f>IF($E$3="","",$E$3+A15-1)</f>
+        <f>IF($B$3="","",$B$3+A15-1)</f>
         <v/>
       </c>
       <c r="C15" s="28" t="n">
@@ -1170,25 +1241,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>She thinks that's junk. It isn't.</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="31" t="inlineStr"/>
-      <c r="H15" s="30" t="n"/>
+      <c r="H15" s="31" t="inlineStr"/>
+      <c r="I15" s="30" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B16" s="29">
-        <f>IF($E$3="","",$E$3+A16-1)</f>
+        <f>IF($B$3="","",$B$3+A16-1)</f>
         <v/>
       </c>
       <c r="C16" s="28" t="n">
@@ -1199,25 +1275,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>No talking. Just cleaning.</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="31" t="inlineStr"/>
-      <c r="H16" s="30" t="n"/>
+      <c r="H16" s="31" t="inlineStr"/>
+      <c r="I16" s="30" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="24" t="n">
         <v>6</v>
       </c>
       <c r="B17" s="25">
-        <f>IF($E$3="","",$E$3+A17-1)</f>
+        <f>IF($B$3="","",$B$3+A17-1)</f>
         <v/>
       </c>
       <c r="C17" s="24" t="n">
@@ -1228,25 +1309,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Same spot, same target. One of these finds it.</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="G17" s="27" t="inlineStr"/>
-      <c r="H17" s="26" t="n"/>
+      <c r="H17" s="27" t="inlineStr"/>
+      <c r="I17" s="26" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="28" t="n">
         <v>7</v>
       </c>
       <c r="B18" s="29">
-        <f>IF($E$3="","",$E$3+A18-1)</f>
+        <f>IF($B$3="","",$B$3+A18-1)</f>
         <v/>
       </c>
       <c r="C18" s="28" t="n">
@@ -1257,25 +1343,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>Give it thirty seconds.</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="31" t="inlineStr"/>
-      <c r="H18" s="30" t="n"/>
+      <c r="H18" s="31" t="inlineStr"/>
+      <c r="I18" s="30" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="28" t="n">
         <v>7</v>
       </c>
       <c r="B19" s="29">
-        <f>IF($E$3="","",$E$3+A19-1)</f>
+        <f>IF($B$3="","",$B$3+A19-1)</f>
         <v/>
       </c>
       <c r="C19" s="28" t="n">
@@ -1286,25 +1377,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>This might be the find of the year.</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="31" t="inlineStr"/>
-      <c r="H19" s="30" t="n"/>
+      <c r="H19" s="31" t="inlineStr"/>
+      <c r="I19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="24" t="n">
         <v>8</v>
       </c>
       <c r="B20" s="25">
-        <f>IF($E$3="","",$E$3+A20-1)</f>
+        <f>IF($B$3="","",$B$3+A20-1)</f>
         <v/>
       </c>
       <c r="C20" s="24" t="n">
@@ -1315,25 +1411,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>Listen to that. That's a good one.</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr"/>
-      <c r="H20" s="26" t="n"/>
+      <c r="H20" s="27" t="inlineStr"/>
+      <c r="I20" s="26" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B21" s="29">
-        <f>IF($E$3="","",$E$3+A21-1)</f>
+        <f>IF($B$3="","",$B$3+A21-1)</f>
         <v/>
       </c>
       <c r="C21" s="28" t="n">
@@ -1344,25 +1445,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
+        <is>
+          <t>This came out of the ground looking like a rock.</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="31" t="inlineStr"/>
-      <c r="H21" s="30" t="n"/>
+      <c r="H21" s="31" t="inlineStr"/>
+      <c r="I21" s="30" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="24" t="n">
         <v>9</v>
       </c>
       <c r="B22" s="25">
-        <f>IF($E$3="","",$E$3+A22-1)</f>
+        <f>IF($B$3="","",$B$3+A22-1)</f>
         <v/>
       </c>
       <c r="C22" s="24" t="n">
@@ -1373,25 +1479,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>Twelve years detecting and this still got me.</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="G22" s="27" t="inlineStr"/>
-      <c r="H22" s="26" t="n"/>
+      <c r="H22" s="27" t="inlineStr"/>
+      <c r="I22" s="26" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="28" t="n">
         <v>9</v>
       </c>
       <c r="B23" s="29">
-        <f>IF($E$3="","",$E$3+A23-1)</f>
+        <f>IF($B$3="","",$B$3+A23-1)</f>
         <v/>
       </c>
       <c r="C23" s="28" t="n">
@@ -1402,25 +1513,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
+        <is>
+          <t>He nearly threw it back.</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="31" t="inlineStr"/>
-      <c r="H23" s="30" t="n"/>
+      <c r="H23" s="31" t="inlineStr"/>
+      <c r="I23" s="30" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B24" s="29">
-        <f>IF($E$3="","",$E$3+A24-1)</f>
+        <f>IF($B$3="","",$B$3+A24-1)</f>
         <v/>
       </c>
       <c r="C24" s="28" t="n">
@@ -1431,25 +1547,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>Before and after, no filter.</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="31" t="inlineStr"/>
-      <c r="H24" s="30" t="n"/>
+      <c r="H24" s="31" t="inlineStr"/>
+      <c r="I24" s="30" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="24" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="25">
-        <f>IF($E$3="","",$E$3+A25-1)</f>
+        <f>IF($B$3="","",$B$3+A25-1)</f>
         <v/>
       </c>
       <c r="C25" s="24" t="n">
@@ -1460,25 +1581,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>The signal was screaming.</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="G25" s="27" t="inlineStr"/>
-      <c r="H25" s="26" t="n"/>
+      <c r="H25" s="27" t="inlineStr"/>
+      <c r="I25" s="26" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="25">
-        <f>IF($E$3="","",$E$3+A26-1)</f>
+        <f>IF($B$3="","",$B$3+A26-1)</f>
         <v/>
       </c>
       <c r="C26" s="24" t="n">
@@ -1489,25 +1615,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
+        <is>
+          <t>Whatever this is, it's deep.</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G26" s="27" t="inlineStr"/>
-      <c r="H26" s="26" t="n"/>
+      <c r="H26" s="27" t="inlineStr"/>
+      <c r="I26" s="26" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="28" t="n">
         <v>11</v>
       </c>
       <c r="B27" s="29">
-        <f>IF($E$3="","",$E$3+A27-1)</f>
+        <f>IF($B$3="","",$B$3+A27-1)</f>
         <v/>
       </c>
       <c r="C27" s="28" t="n">
@@ -1518,25 +1649,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>The first shine is the best part.</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="31" t="inlineStr"/>
-      <c r="H27" s="30" t="n"/>
+      <c r="H27" s="31" t="inlineStr"/>
+      <c r="I27" s="30" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="n">
         <v>12</v>
       </c>
       <c r="B28" s="25">
-        <f>IF($E$3="","",$E$3+A28-1)</f>
+        <f>IF($B$3="","",$B$3+A28-1)</f>
         <v/>
       </c>
       <c r="C28" s="24" t="n">
@@ -1547,25 +1683,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
+        <is>
+          <t>I've never dug one this clean.</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G28" s="27" t="inlineStr"/>
-      <c r="H28" s="26" t="n"/>
+      <c r="H28" s="27" t="inlineStr"/>
+      <c r="I28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="28" t="n">
         <v>12</v>
       </c>
       <c r="B29" s="29">
-        <f>IF($E$3="","",$E$3+A29-1)</f>
+        <f>IF($B$3="","",$B$3+A29-1)</f>
         <v/>
       </c>
       <c r="C29" s="28" t="n">
@@ -1576,25 +1717,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
+        <is>
+          <t>Watch his face when he realises.</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="31" t="inlineStr"/>
-      <c r="H29" s="30" t="n"/>
+      <c r="H29" s="31" t="inlineStr"/>
+      <c r="I29" s="30" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="n">
         <v>13</v>
       </c>
       <c r="B30" s="25">
-        <f>IF($E$3="","",$E$3+A30-1)</f>
+        <f>IF($B$3="","",$B$3+A30-1)</f>
         <v/>
       </c>
       <c r="C30" s="24" t="n">
@@ -1605,25 +1751,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
+        <is>
+          <t>Watch the dirt come off this.</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G30" s="27" t="inlineStr"/>
-      <c r="H30" s="26" t="n"/>
+      <c r="H30" s="27" t="inlineStr"/>
+      <c r="I30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="28" t="n">
         <v>13</v>
       </c>
       <c r="B31" s="29">
-        <f>IF($E$3="","",$E$3+A31-1)</f>
+        <f>IF($B$3="","",$B$3+A31-1)</f>
         <v/>
       </c>
       <c r="C31" s="28" t="n">
@@ -1634,25 +1785,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
+        <is>
+          <t>Green to gold in three minutes.</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="31" t="inlineStr"/>
-      <c r="H31" s="30" t="n"/>
+      <c r="H31" s="31" t="inlineStr"/>
+      <c r="I31" s="30" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="24" t="n">
         <v>14</v>
       </c>
       <c r="B32" s="25">
-        <f>IF($E$3="","",$E$3+A32-1)</f>
+        <f>IF($B$3="","",$B$3+A32-1)</f>
         <v/>
       </c>
       <c r="C32" s="24" t="n">
@@ -1663,25 +1819,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
+        <is>
+          <t>Bottle cap. Bottle cap. Bottle cap. Oh.</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G32" s="27" t="inlineStr"/>
-      <c r="H32" s="26" t="n"/>
+      <c r="H32" s="27" t="inlineStr"/>
+      <c r="I32" s="26" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="24" t="n">
         <v>14</v>
       </c>
       <c r="B33" s="25">
-        <f>IF($E$3="","",$E$3+A33-1)</f>
+        <f>IF($B$3="","",$B$3+A33-1)</f>
         <v/>
       </c>
       <c r="C33" s="24" t="n">
@@ -1692,25 +1853,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>This ground's been hunted a thousand times.</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G33" s="27" t="inlineStr"/>
-      <c r="H33" s="26" t="n"/>
+      <c r="H33" s="27" t="inlineStr"/>
+      <c r="I33" s="26" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="28" t="n">
         <v>15</v>
       </c>
       <c r="B34" s="29">
-        <f>IF($E$3="","",$E$3+A34-1)</f>
+        <f>IF($B$3="","",$B$3+A34-1)</f>
         <v/>
       </c>
       <c r="C34" s="28" t="n">
@@ -1721,25 +1887,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="37" t="inlineStr">
+        <is>
+          <t>Sixty years of dirt. Watch.</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="31" t="inlineStr"/>
-      <c r="H34" s="30" t="n"/>
+      <c r="H34" s="31" t="inlineStr"/>
+      <c r="I34" s="30" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="24" t="n">
         <v>15</v>
       </c>
       <c r="B35" s="25">
-        <f>IF($E$3="","",$E$3+A35-1)</f>
+        <f>IF($B$3="","",$B$3+A35-1)</f>
         <v/>
       </c>
       <c r="C35" s="24" t="n">
@@ -1750,25 +1921,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
+        <is>
+          <t>That tone means it's silver.</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="G35" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G35" s="27" t="inlineStr"/>
-      <c r="H35" s="26" t="n"/>
+      <c r="H35" s="27" t="inlineStr"/>
+      <c r="I35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="24" t="n">
         <v>15</v>
       </c>
       <c r="B36" s="25">
-        <f>IF($E$3="","",$E$3+A36-1)</f>
+        <f>IF($B$3="","",$B$3+A36-1)</f>
         <v/>
       </c>
       <c r="C36" s="24" t="n">
@@ -1779,25 +1955,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
+        <is>
+          <t>One hour on this beach. Counter starts now.</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F36" s="24" t="inlineStr">
+      <c r="G36" s="24" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="26" t="n"/>
+      <c r="H36" s="27" t="inlineStr"/>
+      <c r="I36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="24" t="n">
         <v>16</v>
       </c>
       <c r="B37" s="25">
-        <f>IF($E$3="","",$E$3+A37-1)</f>
+        <f>IF($B$3="","",$B$3+A37-1)</f>
         <v/>
       </c>
       <c r="C37" s="24" t="n">
@@ -1808,25 +1989,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
+        <is>
+          <t>There's something two metres under this field.</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F37" s="24" t="inlineStr">
+      <c r="G37" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="26" t="n"/>
+      <c r="H37" s="27" t="inlineStr"/>
+      <c r="I37" s="26" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="24" t="n">
         <v>16</v>
       </c>
       <c r="B38" s="25">
-        <f>IF($E$3="","",$E$3+A38-1)</f>
+        <f>IF($B$3="","",$B$3+A38-1)</f>
         <v/>
       </c>
       <c r="C38" s="24" t="n">
@@ -1837,25 +2023,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
+        <is>
+          <t>If you hear this, dig it.</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="G38" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="26" t="n"/>
+      <c r="H38" s="27" t="inlineStr"/>
+      <c r="I38" s="26" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="28" t="n">
         <v>16</v>
       </c>
       <c r="B39" s="29">
-        <f>IF($E$3="","",$E$3+A39-1)</f>
+        <f>IF($B$3="","",$B$3+A39-1)</f>
         <v/>
       </c>
       <c r="C39" s="28" t="n">
@@ -1866,25 +2057,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
+        <is>
+          <t>You will not believe what's under this.</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F39" s="28" t="inlineStr">
+      <c r="G39" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="31" t="inlineStr"/>
-      <c r="H39" s="30" t="n"/>
+      <c r="H39" s="31" t="inlineStr"/>
+      <c r="I39" s="30" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="n">
         <v>17</v>
       </c>
       <c r="B40" s="25">
-        <f>IF($E$3="","",$E$3+A40-1)</f>
+        <f>IF($B$3="","",$B$3+A40-1)</f>
         <v/>
       </c>
       <c r="C40" s="24" t="n">
@@ -1895,25 +2091,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
+        <is>
+          <t>The screen says metal. The ground says nothing.</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="G40" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G40" s="27" t="inlineStr"/>
-      <c r="H40" s="26" t="n"/>
+      <c r="H40" s="27" t="inlineStr"/>
+      <c r="I40" s="26" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="24" t="n">
         <v>17</v>
       </c>
       <c r="B41" s="25">
-        <f>IF($E$3="","",$E$3+A41-1)</f>
+        <f>IF($B$3="","",$B$3+A41-1)</f>
         <v/>
       </c>
       <c r="C41" s="24" t="n">
@@ -1924,25 +2125,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="36" t="inlineStr">
+        <is>
+          <t>Sixty minutes. Let's see what this sand is hiding.</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="G41" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G41" s="27" t="inlineStr"/>
-      <c r="H41" s="26" t="n"/>
+      <c r="H41" s="27" t="inlineStr"/>
+      <c r="I41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="24" t="n">
         <v>17</v>
       </c>
       <c r="B42" s="25">
-        <f>IF($E$3="","",$E$3+A42-1)</f>
+        <f>IF($B$3="","",$B$3+A42-1)</f>
         <v/>
       </c>
       <c r="C42" s="24" t="n">
@@ -1953,25 +2159,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
+        <is>
+          <t>Same ground, same target, two very different price tags.</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="G42" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G42" s="27" t="inlineStr"/>
-      <c r="H42" s="26" t="n"/>
+      <c r="H42" s="27" t="inlineStr"/>
+      <c r="I42" s="26" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="28" t="n">
         <v>18</v>
       </c>
       <c r="B43" s="29">
-        <f>IF($E$3="","",$E$3+A43-1)</f>
+        <f>IF($B$3="","",$B$3+A43-1)</f>
         <v/>
       </c>
       <c r="C43" s="28" t="n">
@@ -1982,25 +2193,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
+        <is>
+          <t>No talking. Just cleaning.</t>
+        </is>
+      </c>
+      <c r="F43" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F43" s="28" t="inlineStr">
+      <c r="G43" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="31" t="inlineStr"/>
-      <c r="H43" s="30" t="n"/>
+      <c r="H43" s="31" t="inlineStr"/>
+      <c r="I43" s="30" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="24" t="n">
         <v>18</v>
       </c>
       <c r="B44" s="25">
-        <f>IF($E$3="","",$E$3+A44-1)</f>
+        <f>IF($B$3="","",$B$3+A44-1)</f>
         <v/>
       </c>
       <c r="C44" s="24" t="n">
@@ -2011,25 +2227,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
+        <is>
+          <t>I almost walked past this.</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F44" s="24" t="inlineStr">
+      <c r="G44" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G44" s="27" t="inlineStr"/>
-      <c r="H44" s="26" t="n"/>
+      <c r="H44" s="27" t="inlineStr"/>
+      <c r="I44" s="26" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="24" t="n">
         <v>18</v>
       </c>
       <c r="B45" s="25">
-        <f>IF($E$3="","",$E$3+A45-1)</f>
+        <f>IF($B$3="","",$B$3+A45-1)</f>
         <v/>
       </c>
       <c r="C45" s="24" t="n">
@@ -2040,25 +2261,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>I buried this at four feet. Let's see which one screams.</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="G45" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G45" s="27" t="inlineStr"/>
-      <c r="H45" s="26" t="n"/>
+      <c r="H45" s="27" t="inlineStr"/>
+      <c r="I45" s="26" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="24" t="n">
         <v>19</v>
       </c>
       <c r="B46" s="25">
-        <f>IF($E$3="","",$E$3+A46-1)</f>
+        <f>IF($B$3="","",$B$3+A46-1)</f>
         <v/>
       </c>
       <c r="C46" s="24" t="n">
@@ -2069,25 +2295,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr">
+        <is>
+          <t>One hour, one detector, no cherry-picking.</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="G46" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G46" s="27" t="inlineStr"/>
-      <c r="H46" s="26" t="n"/>
+      <c r="H46" s="27" t="inlineStr"/>
+      <c r="I46" s="26" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="28" t="n">
         <v>19</v>
       </c>
       <c r="B47" s="29">
-        <f>IF($E$3="","",$E$3+A47-1)</f>
+        <f>IF($B$3="","",$B$3+A47-1)</f>
         <v/>
       </c>
       <c r="C47" s="28" t="n">
@@ -2098,25 +2329,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E47" s="37" t="inlineStr">
+        <is>
+          <t>Give it thirty seconds.</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F47" s="28" t="inlineStr">
+      <c r="G47" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="31" t="inlineStr"/>
-      <c r="H47" s="30" t="n"/>
+      <c r="H47" s="31" t="inlineStr"/>
+      <c r="I47" s="30" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="24" t="n">
         <v>19</v>
       </c>
       <c r="B48" s="25">
-        <f>IF($E$3="","",$E$3+A48-1)</f>
+        <f>IF($B$3="","",$B$3+A48-1)</f>
         <v/>
       </c>
       <c r="C48" s="24" t="n">
@@ -2127,25 +2363,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="36" t="inlineStr">
+        <is>
+          <t>Everyone says you can't detect wet salt sand. Let's find out.</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F48" s="24" t="inlineStr">
+      <c r="G48" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G48" s="27" t="inlineStr"/>
-      <c r="H48" s="26" t="n"/>
+      <c r="H48" s="27" t="inlineStr"/>
+      <c r="I48" s="26" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="28" t="n">
         <v>20</v>
       </c>
       <c r="B49" s="29">
-        <f>IF($E$3="","",$E$3+A49-1)</f>
+        <f>IF($B$3="","",$B$3+A49-1)</f>
         <v/>
       </c>
       <c r="C49" s="28" t="n">
@@ -2156,25 +2397,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E49" s="37" t="inlineStr">
+        <is>
+          <t>I've been sent a hundred of these. This one's different.</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F49" s="28" t="inlineStr">
+      <c r="G49" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="31" t="inlineStr"/>
-      <c r="H49" s="30" t="n"/>
+      <c r="H49" s="31" t="inlineStr"/>
+      <c r="I49" s="30" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="28" t="n">
         <v>20</v>
       </c>
       <c r="B50" s="29">
-        <f>IF($E$3="","",$E$3+A50-1)</f>
+        <f>IF($B$3="","",$B$3+A50-1)</f>
         <v/>
       </c>
       <c r="C50" s="28" t="n">
@@ -2185,25 +2431,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E50" s="37" t="inlineStr">
+        <is>
+          <t>This came out of the ground looking like a rock.</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F50" s="28" t="inlineStr">
+      <c r="G50" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="31" t="inlineStr"/>
-      <c r="H50" s="30" t="n"/>
+      <c r="H50" s="31" t="inlineStr"/>
+      <c r="I50" s="30" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="24" t="n">
         <v>20</v>
       </c>
       <c r="B51" s="25">
-        <f>IF($E$3="","",$E$3+A51-1)</f>
+        <f>IF($B$3="","",$B$3+A51-1)</f>
         <v/>
       </c>
       <c r="C51" s="24" t="n">
@@ -2214,25 +2465,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="36" t="inlineStr">
+        <is>
+          <t>This tone costs beginners their best finds.</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="G51" s="24" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="G51" s="27" t="inlineStr"/>
-      <c r="H51" s="26" t="n"/>
+      <c r="H51" s="27" t="inlineStr"/>
+      <c r="I51" s="26" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="28" t="n">
         <v>21</v>
       </c>
       <c r="B52" s="29">
-        <f>IF($E$3="","",$E$3+A52-1)</f>
+        <f>IF($B$3="","",$B$3+A52-1)</f>
         <v/>
       </c>
       <c r="C52" s="28" t="n">
@@ -2243,25 +2499,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E52" s="28" t="inlineStr">
+      <c r="E52" s="37" t="inlineStr">
+        <is>
+          <t>Before and after, no filter.</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F52" s="28" t="inlineStr">
+      <c r="G52" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="31" t="inlineStr"/>
-      <c r="H52" s="30" t="n"/>
+      <c r="H52" s="31" t="inlineStr"/>
+      <c r="I52" s="30" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="28" t="n">
         <v>21</v>
       </c>
       <c r="B53" s="29">
-        <f>IF($E$3="","",$E$3+A53-1)</f>
+        <f>IF($B$3="","",$B$3+A53-1)</f>
         <v/>
       </c>
       <c r="C53" s="28" t="n">
@@ -2272,25 +2533,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E53" s="28" t="inlineStr">
+      <c r="E53" s="37" t="inlineStr">
+        <is>
+          <t>That is not what he thinks it is.</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F53" s="28" t="inlineStr">
+      <c r="G53" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="31" t="inlineStr"/>
-      <c r="H53" s="30" t="n"/>
+      <c r="H53" s="31" t="inlineStr"/>
+      <c r="I53" s="30" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="24" t="n">
         <v>21</v>
       </c>
       <c r="B54" s="25">
-        <f>IF($E$3="","",$E$3+A54-1)</f>
+        <f>IF($B$3="","",$B$3+A54-1)</f>
         <v/>
       </c>
       <c r="C54" s="24" t="n">
@@ -2301,25 +2567,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E54" s="36" t="inlineStr">
+        <is>
+          <t>Comment a number. I'm digging whichever square wins.</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F54" s="24" t="inlineStr">
+      <c r="G54" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G54" s="27" t="inlineStr"/>
-      <c r="H54" s="26" t="n"/>
+      <c r="H54" s="27" t="inlineStr"/>
+      <c r="I54" s="26" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="24" t="n">
         <v>22</v>
       </c>
       <c r="B55" s="25">
-        <f>IF($E$3="","",$E$3+A55-1)</f>
+        <f>IF($B$3="","",$B$3+A55-1)</f>
         <v/>
       </c>
       <c r="C55" s="24" t="n">
@@ -2330,25 +2601,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E55" s="36" t="inlineStr">
+        <is>
+          <t>Iron or silver? Listen again.</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F55" s="24" t="inlineStr">
+      <c r="G55" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G55" s="27" t="inlineStr"/>
-      <c r="H55" s="26" t="n"/>
+      <c r="H55" s="27" t="inlineStr"/>
+      <c r="I55" s="26" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="24" t="n">
         <v>22</v>
       </c>
       <c r="B56" s="25">
-        <f>IF($E$3="","",$E$3+A56-1)</f>
+        <f>IF($B$3="","",$B$3+A56-1)</f>
         <v/>
       </c>
       <c r="C56" s="24" t="n">
@@ -2359,25 +2635,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E56" s="36" t="inlineStr">
+        <is>
+          <t>Two inches down and it's already shining.</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F56" s="24" t="inlineStr">
+      <c r="G56" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G56" s="27" t="inlineStr"/>
-      <c r="H56" s="26" t="n"/>
+      <c r="H56" s="27" t="inlineStr"/>
+      <c r="I56" s="26" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="24" t="n">
         <v>22</v>
       </c>
       <c r="B57" s="25">
-        <f>IF($E$3="","",$E$3+A57-1)</f>
+        <f>IF($B$3="","",$B$3+A57-1)</f>
         <v/>
       </c>
       <c r="C57" s="24" t="n">
@@ -2388,25 +2669,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E57" s="36" t="inlineStr">
+        <is>
+          <t>Your detector isn't broken. It's just shallow.</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="G57" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G57" s="27" t="inlineStr"/>
-      <c r="H57" s="26" t="n"/>
+      <c r="H57" s="27" t="inlineStr"/>
+      <c r="I57" s="26" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="24" t="n">
         <v>23</v>
       </c>
       <c r="B58" s="25">
-        <f>IF($E$3="","",$E$3+A58-1)</f>
+        <f>IF($B$3="","",$B$3+A58-1)</f>
         <v/>
       </c>
       <c r="C58" s="24" t="n">
@@ -2417,25 +2703,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E58" s="36" t="inlineStr">
+        <is>
+          <t>This is what underground actually looks like.</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F58" s="24" t="inlineStr">
+      <c r="G58" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G58" s="27" t="inlineStr"/>
-      <c r="H58" s="26" t="n"/>
+      <c r="H58" s="27" t="inlineStr"/>
+      <c r="I58" s="26" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="n">
         <v>23</v>
       </c>
       <c r="B59" s="25">
-        <f>IF($E$3="","",$E$3+A59-1)</f>
+        <f>IF($B$3="","",$B$3+A59-1)</f>
         <v/>
       </c>
       <c r="C59" s="24" t="n">
@@ -2446,25 +2737,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E59" s="36" t="inlineStr">
+        <is>
+          <t>Everything I find in an hour. Good and bad.</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F59" s="24" t="inlineStr">
+      <c r="G59" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G59" s="27" t="inlineStr"/>
-      <c r="H59" s="26" t="n"/>
+      <c r="H59" s="27" t="inlineStr"/>
+      <c r="I59" s="26" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="28" t="n">
         <v>23</v>
       </c>
       <c r="B60" s="29">
-        <f>IF($E$3="","",$E$3+A60-1)</f>
+        <f>IF($B$3="","",$B$3+A60-1)</f>
         <v/>
       </c>
       <c r="C60" s="28" t="n">
@@ -2475,25 +2771,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E60" s="28" t="inlineStr">
+      <c r="E60" s="37" t="inlineStr">
+        <is>
+          <t>He has no idea what he just dug up.</t>
+        </is>
+      </c>
+      <c r="F60" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F60" s="28" t="inlineStr">
+      <c r="G60" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G60" s="31" t="inlineStr"/>
-      <c r="H60" s="30" t="n"/>
+      <c r="H60" s="31" t="inlineStr"/>
+      <c r="I60" s="30" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="24" t="n">
         <v>24</v>
       </c>
       <c r="B61" s="25">
-        <f>IF($E$3="","",$E$3+A61-1)</f>
+        <f>IF($B$3="","",$B$3+A61-1)</f>
         <v/>
       </c>
       <c r="C61" s="24" t="n">
@@ -2504,25 +2805,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E61" s="24" t="inlineStr">
+      <c r="E61" s="36" t="inlineStr">
+        <is>
+          <t>Before you spend $2,000, watch this.</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F61" s="24" t="inlineStr">
+      <c r="G61" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G61" s="27" t="inlineStr"/>
-      <c r="H61" s="26" t="n"/>
+      <c r="H61" s="27" t="inlineStr"/>
+      <c r="I61" s="26" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="24" t="n">
         <v>24</v>
       </c>
       <c r="B62" s="25">
-        <f>IF($E$3="","",$E$3+A62-1)</f>
+        <f>IF($B$3="","",$B$3+A62-1)</f>
         <v/>
       </c>
       <c r="C62" s="24" t="n">
@@ -2533,25 +2839,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E62" s="24" t="inlineStr">
+      <c r="E62" s="36" t="inlineStr">
+        <is>
+          <t>Nine squares. You choose, I dig.</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F62" s="24" t="inlineStr">
+      <c r="G62" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G62" s="27" t="inlineStr"/>
-      <c r="H62" s="26" t="n"/>
+      <c r="H62" s="27" t="inlineStr"/>
+      <c r="I62" s="26" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="24" t="n">
         <v>24</v>
       </c>
       <c r="B63" s="25">
-        <f>IF($E$3="","",$E$3+A63-1)</f>
+        <f>IF($B$3="","",$B$3+A63-1)</f>
         <v/>
       </c>
       <c r="C63" s="24" t="n">
@@ -2562,25 +2873,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E63" s="24" t="inlineStr">
+      <c r="E63" s="36" t="inlineStr">
+        <is>
+          <t>That's not a bottle cap.</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F63" s="24" t="inlineStr">
+      <c r="G63" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G63" s="27" t="inlineStr"/>
-      <c r="H63" s="26" t="n"/>
+      <c r="H63" s="27" t="inlineStr"/>
+      <c r="I63" s="26" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="28" t="n">
         <v>25</v>
       </c>
       <c r="B64" s="29">
-        <f>IF($E$3="","",$E$3+A64-1)</f>
+        <f>IF($B$3="","",$B$3+A64-1)</f>
         <v/>
       </c>
       <c r="C64" s="28" t="n">
@@ -2591,25 +2907,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E64" s="28" t="inlineStr">
+      <c r="E64" s="37" t="inlineStr">
+        <is>
+          <t>She thinks that's junk. It isn't.</t>
+        </is>
+      </c>
+      <c r="F64" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F64" s="28" t="inlineStr">
+      <c r="G64" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G64" s="31" t="inlineStr"/>
-      <c r="H64" s="30" t="n"/>
+      <c r="H64" s="31" t="inlineStr"/>
+      <c r="I64" s="30" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="24" t="n">
         <v>25</v>
       </c>
       <c r="B65" s="25">
-        <f>IF($E$3="","",$E$3+A65-1)</f>
+        <f>IF($B$3="","",$B$3+A65-1)</f>
         <v/>
       </c>
       <c r="C65" s="24" t="n">
@@ -2620,25 +2941,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E65" s="24" t="inlineStr">
+      <c r="E65" s="36" t="inlineStr">
+        <is>
+          <t>Listen to that. That's a good one.</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F65" s="24" t="inlineStr">
+      <c r="G65" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G65" s="27" t="inlineStr"/>
-      <c r="H65" s="26" t="n"/>
+      <c r="H65" s="27" t="inlineStr"/>
+      <c r="I65" s="26" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="24" t="n">
         <v>25</v>
       </c>
       <c r="B66" s="25">
-        <f>IF($E$3="","",$E$3+A66-1)</f>
+        <f>IF($B$3="","",$B$3+A66-1)</f>
         <v/>
       </c>
       <c r="C66" s="24" t="n">
@@ -2649,25 +2975,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E66" s="24" t="inlineStr">
+      <c r="E66" s="36" t="inlineStr">
+        <is>
+          <t>Pick one. I'll be back tomorrow with what's in it.</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F66" s="24" t="inlineStr">
+      <c r="G66" s="24" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="G66" s="27" t="inlineStr"/>
-      <c r="H66" s="26" t="n"/>
+      <c r="H66" s="27" t="inlineStr"/>
+      <c r="I66" s="26" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="28" t="n">
         <v>26</v>
       </c>
       <c r="B67" s="29">
-        <f>IF($E$3="","",$E$3+A67-1)</f>
+        <f>IF($B$3="","",$B$3+A67-1)</f>
         <v/>
       </c>
       <c r="C67" s="28" t="n">
@@ -2678,25 +3009,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E67" s="28" t="inlineStr">
+      <c r="E67" s="37" t="inlineStr">
+        <is>
+          <t>This might be the find of the year.</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F67" s="28" t="inlineStr">
+      <c r="G67" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G67" s="31" t="inlineStr"/>
-      <c r="H67" s="30" t="n"/>
+      <c r="H67" s="31" t="inlineStr"/>
+      <c r="I67" s="30" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="24" t="n">
         <v>26</v>
       </c>
       <c r="B68" s="25">
-        <f>IF($E$3="","",$E$3+A68-1)</f>
+        <f>IF($B$3="","",$B$3+A68-1)</f>
         <v/>
       </c>
       <c r="C68" s="24" t="n">
@@ -2707,25 +3043,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E68" s="24" t="inlineStr">
+      <c r="E68" s="36" t="inlineStr">
+        <is>
+          <t>Twelve years detecting and this still got me.</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F68" s="24" t="inlineStr">
+      <c r="G68" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G68" s="27" t="inlineStr"/>
-      <c r="H68" s="26" t="n"/>
+      <c r="H68" s="27" t="inlineStr"/>
+      <c r="I68" s="26" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="24" t="n">
         <v>26</v>
       </c>
       <c r="B69" s="25">
-        <f>IF($E$3="","",$E$3+A69-1)</f>
+        <f>IF($B$3="","",$B$3+A69-1)</f>
         <v/>
       </c>
       <c r="C69" s="24" t="n">
@@ -2736,25 +3077,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E69" s="24" t="inlineStr">
+      <c r="E69" s="36" t="inlineStr">
+        <is>
+          <t>$300 versus $10,000, same patch of dirt.</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F69" s="24" t="inlineStr">
+      <c r="G69" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G69" s="27" t="inlineStr"/>
-      <c r="H69" s="26" t="n"/>
+      <c r="H69" s="27" t="inlineStr"/>
+      <c r="I69" s="26" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="28" t="n">
         <v>27</v>
       </c>
       <c r="B70" s="29">
-        <f>IF($E$3="","",$E$3+A70-1)</f>
+        <f>IF($B$3="","",$B$3+A70-1)</f>
         <v/>
       </c>
       <c r="C70" s="28" t="n">
@@ -2765,25 +3111,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E70" s="28" t="inlineStr">
+      <c r="E70" s="37" t="inlineStr">
+        <is>
+          <t>He nearly threw it back.</t>
+        </is>
+      </c>
+      <c r="F70" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F70" s="28" t="inlineStr">
+      <c r="G70" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G70" s="31" t="inlineStr"/>
-      <c r="H70" s="30" t="n"/>
+      <c r="H70" s="31" t="inlineStr"/>
+      <c r="I70" s="30" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="24" t="n">
         <v>27</v>
       </c>
       <c r="B71" s="25">
-        <f>IF($E$3="","",$E$3+A71-1)</f>
+        <f>IF($B$3="","",$B$3+A71-1)</f>
         <v/>
       </c>
       <c r="C71" s="24" t="n">
@@ -2794,25 +3145,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E71" s="24" t="inlineStr">
+      <c r="E71" s="36" t="inlineStr">
+        <is>
+          <t>The cheap one walked straight over it.</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F71" s="24" t="inlineStr">
+      <c r="G71" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G71" s="27" t="inlineStr"/>
-      <c r="H71" s="26" t="n"/>
+      <c r="H71" s="27" t="inlineStr"/>
+      <c r="I71" s="26" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="28" t="n">
         <v>27</v>
       </c>
       <c r="B72" s="29">
-        <f>IF($E$3="","",$E$3+A72-1)</f>
+        <f>IF($B$3="","",$B$3+A72-1)</f>
         <v/>
       </c>
       <c r="C72" s="28" t="n">
@@ -2823,25 +3179,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E72" s="28" t="inlineStr">
+      <c r="E72" s="37" t="inlineStr">
+        <is>
+          <t>The first shine is the best part.</t>
+        </is>
+      </c>
+      <c r="F72" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F72" s="28" t="inlineStr">
+      <c r="G72" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G72" s="31" t="inlineStr"/>
-      <c r="H72" s="30" t="n"/>
+      <c r="H72" s="31" t="inlineStr"/>
+      <c r="I72" s="30" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="24" t="n">
         <v>28</v>
       </c>
       <c r="B73" s="25">
-        <f>IF($E$3="","",$E$3+A73-1)</f>
+        <f>IF($B$3="","",$B$3+A73-1)</f>
         <v/>
       </c>
       <c r="C73" s="24" t="n">
@@ -2852,25 +3213,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E73" s="24" t="inlineStr">
+      <c r="E73" s="36" t="inlineStr">
+        <is>
+          <t>The signal was screaming.</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F73" s="24" t="inlineStr">
+      <c r="G73" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G73" s="27" t="inlineStr"/>
-      <c r="H73" s="26" t="n"/>
+      <c r="H73" s="27" t="inlineStr"/>
+      <c r="I73" s="26" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="24" t="n">
         <v>28</v>
       </c>
       <c r="B74" s="25">
-        <f>IF($E$3="","",$E$3+A74-1)</f>
+        <f>IF($B$3="","",$B$3+A74-1)</f>
         <v/>
       </c>
       <c r="C74" s="24" t="n">
@@ -2881,25 +3247,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E74" s="24" t="inlineStr">
+      <c r="E74" s="36" t="inlineStr">
+        <is>
+          <t>An hour here after a storm. This should be good.</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F74" s="24" t="inlineStr">
+      <c r="G74" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G74" s="27" t="inlineStr"/>
-      <c r="H74" s="26" t="n"/>
+      <c r="H74" s="27" t="inlineStr"/>
+      <c r="I74" s="26" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="24" t="n">
         <v>28</v>
       </c>
       <c r="B75" s="25">
-        <f>IF($E$3="","",$E$3+A75-1)</f>
+        <f>IF($B$3="","",$B$3+A75-1)</f>
         <v/>
       </c>
       <c r="C75" s="24" t="n">
@@ -2910,25 +3281,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E75" s="24" t="inlineStr">
+      <c r="E75" s="36" t="inlineStr">
+        <is>
+          <t>Three detectors, one target, only one is honest.</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F75" s="24" t="inlineStr">
+      <c r="G75" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G75" s="27" t="inlineStr"/>
-      <c r="H75" s="26" t="n"/>
+      <c r="H75" s="27" t="inlineStr"/>
+      <c r="I75" s="26" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="24" t="n">
         <v>29</v>
       </c>
       <c r="B76" s="25">
-        <f>IF($E$3="","",$E$3+A76-1)</f>
+        <f>IF($B$3="","",$B$3+A76-1)</f>
         <v/>
       </c>
       <c r="C76" s="24" t="n">
@@ -2939,25 +3315,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E76" s="24" t="inlineStr">
+      <c r="E76" s="36" t="inlineStr">
+        <is>
+          <t>They told me this ground was dead. Testing that.</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F76" s="24" t="inlineStr">
+      <c r="G76" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G76" s="27" t="inlineStr"/>
-      <c r="H76" s="26" t="n"/>
+      <c r="H76" s="27" t="inlineStr"/>
+      <c r="I76" s="26" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="24" t="n">
         <v>29</v>
       </c>
       <c r="B77" s="25">
-        <f>IF($E$3="","",$E$3+A77-1)</f>
+        <f>IF($B$3="","",$B$3+A77-1)</f>
         <v/>
       </c>
       <c r="C77" s="24" t="n">
@@ -2968,25 +3349,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E77" s="24" t="inlineStr">
+      <c r="E77" s="36" t="inlineStr">
+        <is>
+          <t>Whatever this is, it's deep.</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F77" s="24" t="inlineStr">
+      <c r="G77" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G77" s="27" t="inlineStr"/>
-      <c r="H77" s="26" t="n"/>
+      <c r="H77" s="27" t="inlineStr"/>
+      <c r="I77" s="26" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="24" t="n">
         <v>29</v>
       </c>
       <c r="B78" s="25">
-        <f>IF($E$3="","",$E$3+A78-1)</f>
+        <f>IF($B$3="","",$B$3+A78-1)</f>
         <v/>
       </c>
       <c r="C78" s="24" t="n">
@@ -2997,25 +3383,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E78" s="24" t="inlineStr">
+      <c r="E78" s="36" t="inlineStr">
+        <is>
+          <t>How much can one hour actually pay?</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F78" s="24" t="inlineStr">
+      <c r="G78" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G78" s="27" t="inlineStr"/>
-      <c r="H78" s="26" t="n"/>
+      <c r="H78" s="27" t="inlineStr"/>
+      <c r="I78" s="26" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="24" t="n">
         <v>30</v>
       </c>
       <c r="B79" s="25">
-        <f>IF($E$3="","",$E$3+A79-1)</f>
+        <f>IF($B$3="","",$B$3+A79-1)</f>
         <v/>
       </c>
       <c r="C79" s="24" t="n">
@@ -3026,25 +3417,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E79" s="24" t="inlineStr">
+      <c r="E79" s="36" t="inlineStr">
+        <is>
+          <t>I've never dug one this clean.</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F79" s="24" t="inlineStr">
+      <c r="G79" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G79" s="27" t="inlineStr"/>
-      <c r="H79" s="26" t="n"/>
+      <c r="H79" s="27" t="inlineStr"/>
+      <c r="I79" s="26" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="24" t="n">
         <v>30</v>
       </c>
       <c r="B80" s="25">
-        <f>IF($E$3="","",$E$3+A80-1)</f>
+        <f>IF($B$3="","",$B$3+A80-1)</f>
         <v/>
       </c>
       <c r="C80" s="24" t="n">
@@ -3055,25 +3451,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E80" s="24" t="inlineStr">
+      <c r="E80" s="36" t="inlineStr">
+        <is>
+          <t>Half of you said square four. So square four it is.</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F80" s="24" t="inlineStr">
+      <c r="G80" s="24" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="G80" s="27" t="inlineStr"/>
-      <c r="H80" s="26" t="n"/>
+      <c r="H80" s="27" t="inlineStr"/>
+      <c r="I80" s="26" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="28" t="n">
         <v>30</v>
       </c>
       <c r="B81" s="29">
-        <f>IF($E$3="","",$E$3+A81-1)</f>
+        <f>IF($B$3="","",$B$3+A81-1)</f>
         <v/>
       </c>
       <c r="C81" s="28" t="n">
@@ -3084,25 +3485,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E81" s="28" t="inlineStr">
+      <c r="E81" s="37" t="inlineStr">
+        <is>
+          <t>Green to gold in three minutes.</t>
+        </is>
+      </c>
+      <c r="F81" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F81" s="28" t="inlineStr">
+      <c r="G81" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="31" t="inlineStr"/>
-      <c r="H81" s="30" t="n"/>
+      <c r="H81" s="31" t="inlineStr"/>
+      <c r="I81" s="30" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="24" t="n">
         <v>31</v>
       </c>
       <c r="B82" s="25">
-        <f>IF($E$3="","",$E$3+A82-1)</f>
+        <f>IF($B$3="","",$B$3+A82-1)</f>
         <v/>
       </c>
       <c r="C82" s="24" t="n">
@@ -3113,20 +3519,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E82" s="24" t="inlineStr">
+      <c r="E82" s="36" t="inlineStr">
+        <is>
+          <t>Third day on this creek. Today it finally paid.</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F82" s="24" t="inlineStr">
+      <c r="G82" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G82" s="27" t="inlineStr"/>
-      <c r="H82" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H82" s="27" t="inlineStr"/>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3546,7 @@
         <v>31</v>
       </c>
       <c r="B83" s="25">
-        <f>IF($E$3="","",$E$3+A83-1)</f>
+        <f>IF($B$3="","",$B$3+A83-1)</f>
         <v/>
       </c>
       <c r="C83" s="24" t="n">
@@ -3146,25 +3557,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E83" s="24" t="inlineStr">
+      <c r="E83" s="36" t="inlineStr">
+        <is>
+          <t>Watch the dirt come off this.</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F83" s="24" t="inlineStr">
+      <c r="G83" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G83" s="27" t="inlineStr"/>
-      <c r="H83" s="26" t="n"/>
+      <c r="H83" s="27" t="inlineStr"/>
+      <c r="I83" s="26" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="24" t="n">
         <v>31</v>
       </c>
       <c r="B84" s="25">
-        <f>IF($E$3="","",$E$3+A84-1)</f>
+        <f>IF($B$3="","",$B$3+A84-1)</f>
         <v/>
       </c>
       <c r="C84" s="24" t="n">
@@ -3175,25 +3591,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E84" s="24" t="inlineStr">
+      <c r="E84" s="36" t="inlineStr">
+        <is>
+          <t>That flutter means it's sitting on edge.</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F84" s="24" t="inlineStr">
+      <c r="G84" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G84" s="27" t="inlineStr"/>
-      <c r="H84" s="26" t="n"/>
+      <c r="H84" s="27" t="inlineStr"/>
+      <c r="I84" s="26" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="24" t="n">
         <v>32</v>
       </c>
       <c r="B85" s="25">
-        <f>IF($E$3="","",$E$3+A85-1)</f>
+        <f>IF($B$3="","",$B$3+A85-1)</f>
         <v/>
       </c>
       <c r="C85" s="24" t="n">
@@ -3204,25 +3625,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E85" s="24" t="inlineStr">
+      <c r="E85" s="36" t="inlineStr">
+        <is>
+          <t>Bottle cap. Bottle cap. Bottle cap. Oh.</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F85" s="24" t="inlineStr">
+      <c r="G85" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G85" s="27" t="inlineStr"/>
-      <c r="H85" s="26" t="n"/>
+      <c r="H85" s="27" t="inlineStr"/>
+      <c r="I85" s="26" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="28" t="n">
         <v>32</v>
       </c>
       <c r="B86" s="29">
-        <f>IF($E$3="","",$E$3+A86-1)</f>
+        <f>IF($B$3="","",$B$3+A86-1)</f>
         <v/>
       </c>
       <c r="C86" s="28" t="n">
@@ -3233,25 +3659,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E86" s="28" t="inlineStr">
+      <c r="E86" s="37" t="inlineStr">
+        <is>
+          <t>Watch his face when he realises.</t>
+        </is>
+      </c>
+      <c r="F86" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F86" s="28" t="inlineStr">
+      <c r="G86" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="31" t="inlineStr"/>
-      <c r="H86" s="30" t="n"/>
+      <c r="H86" s="31" t="inlineStr"/>
+      <c r="I86" s="30" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="28" t="n">
         <v>32</v>
       </c>
       <c r="B87" s="29">
-        <f>IF($E$3="","",$E$3+A87-1)</f>
+        <f>IF($B$3="","",$B$3+A87-1)</f>
         <v/>
       </c>
       <c r="C87" s="28" t="n">
@@ -3262,25 +3693,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E87" s="28" t="inlineStr">
+      <c r="E87" s="37" t="inlineStr">
+        <is>
+          <t>Sixty years of dirt. Watch.</t>
+        </is>
+      </c>
+      <c r="F87" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F87" s="28" t="inlineStr">
+      <c r="G87" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G87" s="31" t="inlineStr"/>
-      <c r="H87" s="30" t="n"/>
+      <c r="H87" s="31" t="inlineStr"/>
+      <c r="I87" s="30" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="24" t="n">
         <v>33</v>
       </c>
       <c r="B88" s="25">
-        <f>IF($E$3="","",$E$3+A88-1)</f>
+        <f>IF($B$3="","",$B$3+A88-1)</f>
         <v/>
       </c>
       <c r="C88" s="24" t="n">
@@ -3291,25 +3727,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E88" s="24" t="inlineStr">
+      <c r="E88" s="36" t="inlineStr">
+        <is>
+          <t>This ground's been hunted a thousand times.</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F88" s="24" t="inlineStr">
+      <c r="G88" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G88" s="27" t="inlineStr"/>
-      <c r="H88" s="26" t="n"/>
+      <c r="H88" s="27" t="inlineStr"/>
+      <c r="I88" s="26" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="24" t="n">
         <v>33</v>
       </c>
       <c r="B89" s="25">
-        <f>IF($E$3="","",$E$3+A89-1)</f>
+        <f>IF($B$3="","",$B$3+A89-1)</f>
         <v/>
       </c>
       <c r="C89" s="24" t="n">
@@ -3320,25 +3761,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E89" s="24" t="inlineStr">
+      <c r="E89" s="36" t="inlineStr">
+        <is>
+          <t>The cheaper one won. I did not expect that.</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F89" s="24" t="inlineStr">
+      <c r="G89" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G89" s="27" t="inlineStr"/>
-      <c r="H89" s="26" t="n"/>
+      <c r="H89" s="27" t="inlineStr"/>
+      <c r="I89" s="26" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="24" t="n">
         <v>33</v>
       </c>
       <c r="B90" s="25">
-        <f>IF($E$3="","",$E$3+A90-1)</f>
+        <f>IF($B$3="","",$B$3+A90-1)</f>
         <v/>
       </c>
       <c r="C90" s="24" t="n">
@@ -3349,25 +3795,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E90" s="24" t="inlineStr">
+      <c r="E90" s="36" t="inlineStr">
+        <is>
+          <t>One sound, two very different outcomes.</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F90" s="24" t="inlineStr">
+      <c r="G90" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G90" s="27" t="inlineStr"/>
-      <c r="H90" s="26" t="n"/>
+      <c r="H90" s="27" t="inlineStr"/>
+      <c r="I90" s="26" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="24" t="n">
         <v>34</v>
       </c>
       <c r="B91" s="25">
-        <f>IF($E$3="","",$E$3+A91-1)</f>
+        <f>IF($B$3="","",$B$3+A91-1)</f>
         <v/>
       </c>
       <c r="C91" s="24" t="n">
@@ -3378,25 +3829,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E91" s="24" t="inlineStr">
+      <c r="E91" s="36" t="inlineStr">
+        <is>
+          <t>That tone means it's silver.</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F91" s="24" t="inlineStr">
+      <c r="G91" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G91" s="27" t="inlineStr"/>
-      <c r="H91" s="26" t="n"/>
+      <c r="H91" s="27" t="inlineStr"/>
+      <c r="I91" s="26" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="28" t="n">
         <v>34</v>
       </c>
       <c r="B92" s="29">
-        <f>IF($E$3="","",$E$3+A92-1)</f>
+        <f>IF($B$3="","",$B$3+A92-1)</f>
         <v/>
       </c>
       <c r="C92" s="28" t="n">
@@ -3407,25 +3863,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E92" s="28" t="inlineStr">
+      <c r="E92" s="37" t="inlineStr">
+        <is>
+          <t>You will not believe what's under this.</t>
+        </is>
+      </c>
+      <c r="F92" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F92" s="28" t="inlineStr">
+      <c r="G92" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G92" s="31" t="inlineStr"/>
-      <c r="H92" s="30" t="n"/>
+      <c r="H92" s="31" t="inlineStr"/>
+      <c r="I92" s="30" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="28" t="n">
         <v>34</v>
       </c>
       <c r="B93" s="29">
-        <f>IF($E$3="","",$E$3+A93-1)</f>
+        <f>IF($B$3="","",$B$3+A93-1)</f>
         <v/>
       </c>
       <c r="C93" s="28" t="n">
@@ -3436,25 +3897,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E93" s="28" t="inlineStr">
+      <c r="E93" s="37" t="inlineStr">
+        <is>
+          <t>I've been sent a hundred of these. This one's different.</t>
+        </is>
+      </c>
+      <c r="F93" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F93" s="28" t="inlineStr">
+      <c r="G93" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G93" s="31" t="inlineStr"/>
-      <c r="H93" s="30" t="n"/>
+      <c r="H93" s="31" t="inlineStr"/>
+      <c r="I93" s="30" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="24" t="n">
         <v>35</v>
       </c>
       <c r="B94" s="25">
-        <f>IF($E$3="","",$E$3+A94-1)</f>
+        <f>IF($B$3="","",$B$3+A94-1)</f>
         <v/>
       </c>
       <c r="C94" s="24" t="n">
@@ -3465,25 +3931,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E94" s="24" t="inlineStr">
+      <c r="E94" s="36" t="inlineStr">
+        <is>
+          <t>I almost walked past this.</t>
+        </is>
+      </c>
+      <c r="F94" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F94" s="24" t="inlineStr">
+      <c r="G94" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G94" s="27" t="inlineStr"/>
-      <c r="H94" s="26" t="n"/>
+      <c r="H94" s="27" t="inlineStr"/>
+      <c r="I94" s="26" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="24" t="n">
         <v>35</v>
       </c>
       <c r="B95" s="25">
-        <f>IF($E$3="","",$E$3+A95-1)</f>
+        <f>IF($B$3="","",$B$3+A95-1)</f>
         <v/>
       </c>
       <c r="C95" s="24" t="n">
@@ -3494,25 +3965,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E95" s="24" t="inlineStr">
+      <c r="E95" s="36" t="inlineStr">
+        <is>
+          <t>Learn this tone and you'll double your finds.</t>
+        </is>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F95" s="24" t="inlineStr">
+      <c r="G95" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G95" s="27" t="inlineStr"/>
-      <c r="H95" s="26" t="n"/>
+      <c r="H95" s="27" t="inlineStr"/>
+      <c r="I95" s="26" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="24" t="n">
         <v>35</v>
       </c>
       <c r="B96" s="25">
-        <f>IF($E$3="","",$E$3+A96-1)</f>
+        <f>IF($B$3="","",$B$3+A96-1)</f>
         <v/>
       </c>
       <c r="C96" s="24" t="n">
@@ -3523,25 +3999,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E96" s="24" t="inlineStr">
+      <c r="E96" s="36" t="inlineStr">
+        <is>
+          <t>Your detector is telling you something. Here's what.</t>
+        </is>
+      </c>
+      <c r="F96" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F96" s="24" t="inlineStr">
+      <c r="G96" s="24" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="G96" s="27" t="inlineStr"/>
-      <c r="H96" s="26" t="n"/>
+      <c r="H96" s="27" t="inlineStr"/>
+      <c r="I96" s="26" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="24" t="n">
         <v>36</v>
       </c>
       <c r="B97" s="25">
-        <f>IF($E$3="","",$E$3+A97-1)</f>
+        <f>IF($B$3="","",$B$3+A97-1)</f>
         <v/>
       </c>
       <c r="C97" s="24" t="n">
@@ -3552,20 +4033,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E97" s="24" t="inlineStr">
+      <c r="E97" s="36" t="inlineStr">
+        <is>
+          <t>That's gold. That's actually gold.</t>
+        </is>
+      </c>
+      <c r="F97" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F97" s="24" t="inlineStr">
+      <c r="G97" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G97" s="27" t="inlineStr"/>
-      <c r="H97" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H97" s="27" t="inlineStr"/>
+      <c r="I97" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -3574,7 +4060,7 @@
         <v>36</v>
       </c>
       <c r="B98" s="29">
-        <f>IF($E$3="","",$E$3+A98-1)</f>
+        <f>IF($B$3="","",$B$3+A98-1)</f>
         <v/>
       </c>
       <c r="C98" s="28" t="n">
@@ -3585,25 +4071,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E98" s="28" t="inlineStr">
+      <c r="E98" s="37" t="inlineStr">
+        <is>
+          <t>No talking. Just cleaning.</t>
+        </is>
+      </c>
+      <c r="F98" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F98" s="28" t="inlineStr">
+      <c r="G98" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G98" s="31" t="inlineStr"/>
-      <c r="H98" s="30" t="n"/>
+      <c r="H98" s="31" t="inlineStr"/>
+      <c r="I98" s="30" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="24" t="n">
         <v>36</v>
       </c>
       <c r="B99" s="25">
-        <f>IF($E$3="","",$E$3+A99-1)</f>
+        <f>IF($B$3="","",$B$3+A99-1)</f>
         <v/>
       </c>
       <c r="C99" s="24" t="n">
@@ -3614,25 +4105,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="E99" s="36" t="inlineStr">
+        <is>
+          <t>You picked it. Now I have to dig it.</t>
+        </is>
+      </c>
+      <c r="F99" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F99" s="24" t="inlineStr">
+      <c r="G99" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G99" s="27" t="inlineStr"/>
-      <c r="H99" s="26" t="n"/>
+      <c r="H99" s="27" t="inlineStr"/>
+      <c r="I99" s="26" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="24" t="n">
         <v>36</v>
       </c>
       <c r="B100" s="25">
-        <f>IF($E$3="","",$E$3+A100-1)</f>
+        <f>IF($B$3="","",$B$3+A100-1)</f>
         <v/>
       </c>
       <c r="C100" s="24" t="n">
@@ -3643,25 +4139,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E100" s="24" t="inlineStr">
+      <c r="E100" s="36" t="inlineStr">
+        <is>
+          <t>Most people walk away from this sound. Don't.</t>
+        </is>
+      </c>
+      <c r="F100" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F100" s="24" t="inlineStr">
+      <c r="G100" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G100" s="27" t="inlineStr"/>
-      <c r="H100" s="26" t="n"/>
+      <c r="H100" s="27" t="inlineStr"/>
+      <c r="I100" s="26" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="24" t="n">
         <v>37</v>
       </c>
       <c r="B101" s="25">
-        <f>IF($E$3="","",$E$3+A101-1)</f>
+        <f>IF($B$3="","",$B$3+A101-1)</f>
         <v/>
       </c>
       <c r="C101" s="24" t="n">
@@ -3672,25 +4173,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E101" s="24" t="inlineStr">
+      <c r="E101" s="36" t="inlineStr">
+        <is>
+          <t>Timer's on. Let's go.</t>
+        </is>
+      </c>
+      <c r="F101" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F101" s="24" t="inlineStr">
+      <c r="G101" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G101" s="27" t="inlineStr"/>
-      <c r="H101" s="26" t="n"/>
+      <c r="H101" s="27" t="inlineStr"/>
+      <c r="I101" s="26" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="28" t="n">
         <v>37</v>
       </c>
       <c r="B102" s="29">
-        <f>IF($E$3="","",$E$3+A102-1)</f>
+        <f>IF($B$3="","",$B$3+A102-1)</f>
         <v/>
       </c>
       <c r="C102" s="28" t="n">
@@ -3701,25 +4207,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E102" s="28" t="inlineStr">
+      <c r="E102" s="37" t="inlineStr">
+        <is>
+          <t>Give it thirty seconds.</t>
+        </is>
+      </c>
+      <c r="F102" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F102" s="28" t="inlineStr">
+      <c r="G102" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G102" s="31" t="inlineStr"/>
-      <c r="H102" s="30" t="n"/>
+      <c r="H102" s="31" t="inlineStr"/>
+      <c r="I102" s="30" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="24" t="n">
         <v>37</v>
       </c>
       <c r="B103" s="25">
-        <f>IF($E$3="","",$E$3+A103-1)</f>
+        <f>IF($B$3="","",$B$3+A103-1)</f>
         <v/>
       </c>
       <c r="C103" s="24" t="n">
@@ -3730,25 +4241,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E103" s="24" t="inlineStr">
+      <c r="E103" s="36" t="inlineStr">
+        <is>
+          <t>Two inches down and it's already shining.</t>
+        </is>
+      </c>
+      <c r="F103" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F103" s="24" t="inlineStr">
+      <c r="G103" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G103" s="27" t="inlineStr"/>
-      <c r="H103" s="26" t="n"/>
+      <c r="H103" s="27" t="inlineStr"/>
+      <c r="I103" s="26" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="24" t="n">
         <v>37</v>
       </c>
       <c r="B104" s="25">
-        <f>IF($E$3="","",$E$3+A104-1)</f>
+        <f>IF($B$3="","",$B$3+A104-1)</f>
         <v/>
       </c>
       <c r="C104" s="24" t="n">
@@ -3759,25 +4275,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E104" s="24" t="inlineStr">
+      <c r="E104" s="36" t="inlineStr">
+        <is>
+          <t>That red blob is eight feet down.</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F104" s="24" t="inlineStr">
+      <c r="G104" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G104" s="27" t="inlineStr"/>
-      <c r="H104" s="26" t="n"/>
+      <c r="H104" s="27" t="inlineStr"/>
+      <c r="I104" s="26" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="24" t="n">
         <v>38</v>
       </c>
       <c r="B105" s="25">
-        <f>IF($E$3="","",$E$3+A105-1)</f>
+        <f>IF($B$3="","",$B$3+A105-1)</f>
         <v/>
       </c>
       <c r="C105" s="24" t="n">
@@ -3788,25 +4309,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E105" s="24" t="inlineStr">
+      <c r="E105" s="36" t="inlineStr">
+        <is>
+          <t>One hour on this beach. Counter starts now.</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F105" s="24" t="inlineStr">
+      <c r="G105" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G105" s="27" t="inlineStr"/>
-      <c r="H105" s="26" t="n"/>
+      <c r="H105" s="27" t="inlineStr"/>
+      <c r="I105" s="26" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="28" t="n">
         <v>38</v>
       </c>
       <c r="B106" s="29">
-        <f>IF($E$3="","",$E$3+A106-1)</f>
+        <f>IF($B$3="","",$B$3+A106-1)</f>
         <v/>
       </c>
       <c r="C106" s="28" t="n">
@@ -3817,25 +4343,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E106" s="28" t="inlineStr">
+      <c r="E106" s="37" t="inlineStr">
+        <is>
+          <t>That is not what he thinks it is.</t>
+        </is>
+      </c>
+      <c r="F106" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F106" s="28" t="inlineStr">
+      <c r="G106" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G106" s="31" t="inlineStr"/>
-      <c r="H106" s="30" t="n"/>
+      <c r="H106" s="31" t="inlineStr"/>
+      <c r="I106" s="30" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="24" t="n">
         <v>38</v>
       </c>
       <c r="B107" s="25">
-        <f>IF($E$3="","",$E$3+A107-1)</f>
+        <f>IF($B$3="","",$B$3+A107-1)</f>
         <v/>
       </c>
       <c r="C107" s="24" t="n">
@@ -3846,25 +4377,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E107" s="24" t="inlineStr">
+      <c r="E107" s="36" t="inlineStr">
+        <is>
+          <t>Which one would you actually buy?</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F107" s="24" t="inlineStr">
+      <c r="G107" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G107" s="27" t="inlineStr"/>
-      <c r="H107" s="26" t="n"/>
+      <c r="H107" s="27" t="inlineStr"/>
+      <c r="I107" s="26" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="24" t="n">
         <v>38</v>
       </c>
       <c r="B108" s="25">
-        <f>IF($E$3="","",$E$3+A108-1)</f>
+        <f>IF($B$3="","",$B$3+A108-1)</f>
         <v/>
       </c>
       <c r="C108" s="24" t="n">
@@ -3875,25 +4411,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E108" s="24" t="inlineStr">
+      <c r="E108" s="36" t="inlineStr">
+        <is>
+          <t>Most detectorists never see this screen.</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F108" s="24" t="inlineStr">
+      <c r="G108" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G108" s="27" t="inlineStr"/>
-      <c r="H108" s="26" t="n"/>
+      <c r="H108" s="27" t="inlineStr"/>
+      <c r="I108" s="26" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="28" t="n">
         <v>39</v>
       </c>
       <c r="B109" s="29">
-        <f>IF($E$3="","",$E$3+A109-1)</f>
+        <f>IF($B$3="","",$B$3+A109-1)</f>
         <v/>
       </c>
       <c r="C109" s="28" t="n">
@@ -3904,25 +4445,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E109" s="28" t="inlineStr">
+      <c r="E109" s="37" t="inlineStr">
+        <is>
+          <t>This came out of the ground looking like a rock.</t>
+        </is>
+      </c>
+      <c r="F109" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F109" s="28" t="inlineStr">
+      <c r="G109" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G109" s="31" t="inlineStr"/>
-      <c r="H109" s="30" t="n"/>
+      <c r="H109" s="31" t="inlineStr"/>
+      <c r="I109" s="30" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="24" t="n">
         <v>39</v>
       </c>
       <c r="B110" s="25">
-        <f>IF($E$3="","",$E$3+A110-1)</f>
+        <f>IF($B$3="","",$B$3+A110-1)</f>
         <v/>
       </c>
       <c r="C110" s="24" t="n">
@@ -3933,25 +4479,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E110" s="24" t="inlineStr">
+      <c r="E110" s="36" t="inlineStr">
+        <is>
+          <t>Does coil size actually matter? Real test.</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F110" s="24" t="inlineStr">
+      <c r="G110" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G110" s="27" t="inlineStr"/>
-      <c r="H110" s="26" t="n"/>
+      <c r="H110" s="27" t="inlineStr"/>
+      <c r="I110" s="26" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="24" t="n">
         <v>39</v>
       </c>
       <c r="B111" s="25">
-        <f>IF($E$3="","",$E$3+A111-1)</f>
+        <f>IF($B$3="","",$B$3+A111-1)</f>
         <v/>
       </c>
       <c r="C111" s="24" t="n">
@@ -3962,25 +4513,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E111" s="24" t="inlineStr">
+      <c r="E111" s="36" t="inlineStr">
+        <is>
+          <t>That's not a bottle cap.</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F111" s="24" t="inlineStr">
+      <c r="G111" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G111" s="27" t="inlineStr"/>
-      <c r="H111" s="26" t="n"/>
+      <c r="H111" s="27" t="inlineStr"/>
+      <c r="I111" s="26" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="24" t="n">
         <v>39</v>
       </c>
       <c r="B112" s="25">
-        <f>IF($E$3="","",$E$3+A112-1)</f>
+        <f>IF($B$3="","",$B$3+A112-1)</f>
         <v/>
       </c>
       <c r="C112" s="24" t="n">
@@ -3991,20 +4547,25 @@
           <t>05 Ring Recovery</t>
         </is>
       </c>
-      <c r="E112" s="24" t="inlineStr">
+      <c r="E112" s="36" t="inlineStr">
+        <is>
+          <t>She lost it in this lake eleven years ago.</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F112" s="24" t="inlineStr">
+      <c r="G112" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G112" s="27" t="inlineStr"/>
-      <c r="H112" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H112" s="27" t="inlineStr"/>
+      <c r="I112" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4574,7 @@
         <v>40</v>
       </c>
       <c r="B113" s="25">
-        <f>IF($E$3="","",$E$3+A113-1)</f>
+        <f>IF($B$3="","",$B$3+A113-1)</f>
         <v/>
       </c>
       <c r="C113" s="24" t="n">
@@ -4024,25 +4585,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E113" s="24" t="inlineStr">
+      <c r="E113" s="36" t="inlineStr">
+        <is>
+          <t>Listen to that. That's a good one.</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F113" s="24" t="inlineStr">
+      <c r="G113" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G113" s="27" t="inlineStr"/>
-      <c r="H113" s="26" t="n"/>
+      <c r="H113" s="27" t="inlineStr"/>
+      <c r="I113" s="26" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="24" t="n">
         <v>40</v>
       </c>
       <c r="B114" s="25">
-        <f>IF($E$3="","",$E$3+A114-1)</f>
+        <f>IF($B$3="","",$B$3+A114-1)</f>
         <v/>
       </c>
       <c r="C114" s="24" t="n">
@@ -4053,25 +4619,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E114" s="24" t="inlineStr">
+      <c r="E114" s="36" t="inlineStr">
+        <is>
+          <t>If your detector goes quiet here, it's lying to you.</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F114" s="24" t="inlineStr">
+      <c r="G114" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G114" s="27" t="inlineStr"/>
-      <c r="H114" s="26" t="n"/>
+      <c r="H114" s="27" t="inlineStr"/>
+      <c r="I114" s="26" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="28" t="n">
         <v>40</v>
       </c>
       <c r="B115" s="29">
-        <f>IF($E$3="","",$E$3+A115-1)</f>
+        <f>IF($B$3="","",$B$3+A115-1)</f>
         <v/>
       </c>
       <c r="C115" s="28" t="n">
@@ -4082,25 +4653,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E115" s="28" t="inlineStr">
+      <c r="E115" s="37" t="inlineStr">
+        <is>
+          <t>He has no idea what he just dug up.</t>
+        </is>
+      </c>
+      <c r="F115" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F115" s="28" t="inlineStr">
+      <c r="G115" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G115" s="31" t="inlineStr"/>
-      <c r="H115" s="30" t="n"/>
+      <c r="H115" s="31" t="inlineStr"/>
+      <c r="I115" s="30" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="24" t="n">
         <v>40</v>
       </c>
       <c r="B116" s="25">
-        <f>IF($E$3="","",$E$3+A116-1)</f>
+        <f>IF($B$3="","",$B$3+A116-1)</f>
         <v/>
       </c>
       <c r="C116" s="24" t="n">
@@ -4111,25 +4687,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E116" s="24" t="inlineStr">
+      <c r="E116" s="36" t="inlineStr">
+        <is>
+          <t>If you hear this, dig it.</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F116" s="24" t="inlineStr">
+      <c r="G116" s="24" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="G116" s="27" t="inlineStr"/>
-      <c r="H116" s="26" t="n"/>
+      <c r="H116" s="27" t="inlineStr"/>
+      <c r="I116" s="26" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="24" t="n">
         <v>41</v>
       </c>
       <c r="B117" s="25">
-        <f>IF($E$3="","",$E$3+A117-1)</f>
+        <f>IF($B$3="","",$B$3+A117-1)</f>
         <v/>
       </c>
       <c r="C117" s="24" t="n">
@@ -4140,25 +4721,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E117" s="24" t="inlineStr">
+      <c r="E117" s="36" t="inlineStr">
+        <is>
+          <t>Twelve years detecting and this still got me.</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F117" s="24" t="inlineStr">
+      <c r="G117" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G117" s="27" t="inlineStr"/>
-      <c r="H117" s="26" t="n"/>
+      <c r="H117" s="27" t="inlineStr"/>
+      <c r="I117" s="26" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="28" t="n">
         <v>41</v>
       </c>
       <c r="B118" s="29">
-        <f>IF($E$3="","",$E$3+A118-1)</f>
+        <f>IF($B$3="","",$B$3+A118-1)</f>
         <v/>
       </c>
       <c r="C118" s="28" t="n">
@@ -4169,25 +4755,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E118" s="28" t="inlineStr">
+      <c r="E118" s="37" t="inlineStr">
+        <is>
+          <t>She thinks that's junk. It isn't.</t>
+        </is>
+      </c>
+      <c r="F118" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F118" s="28" t="inlineStr">
+      <c r="G118" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G118" s="31" t="inlineStr"/>
-      <c r="H118" s="30" t="n"/>
+      <c r="H118" s="31" t="inlineStr"/>
+      <c r="I118" s="30" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="24" t="n">
         <v>41</v>
       </c>
       <c r="B119" s="25">
-        <f>IF($E$3="","",$E$3+A119-1)</f>
+        <f>IF($B$3="","",$B$3+A119-1)</f>
         <v/>
       </c>
       <c r="C119" s="24" t="n">
@@ -4198,25 +4789,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E119" s="24" t="inlineStr">
+      <c r="E119" s="36" t="inlineStr">
+        <is>
+          <t>This tone costs beginners their best finds.</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F119" s="24" t="inlineStr">
+      <c r="G119" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G119" s="27" t="inlineStr"/>
-      <c r="H119" s="26" t="n"/>
+      <c r="H119" s="27" t="inlineStr"/>
+      <c r="I119" s="26" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="24" t="n">
         <v>41</v>
       </c>
       <c r="B120" s="25">
-        <f>IF($E$3="","",$E$3+A120-1)</f>
+        <f>IF($B$3="","",$B$3+A120-1)</f>
         <v/>
       </c>
       <c r="C120" s="24" t="n">
@@ -4227,25 +4823,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E120" s="24" t="inlineStr">
+      <c r="E120" s="36" t="inlineStr">
+        <is>
+          <t>Last time you chose wrong. Try again.</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F120" s="24" t="inlineStr">
+      <c r="G120" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G120" s="27" t="inlineStr"/>
-      <c r="H120" s="26" t="n"/>
+      <c r="H120" s="27" t="inlineStr"/>
+      <c r="I120" s="26" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="28" t="n">
         <v>42</v>
       </c>
       <c r="B121" s="29">
-        <f>IF($E$3="","",$E$3+A121-1)</f>
+        <f>IF($B$3="","",$B$3+A121-1)</f>
         <v/>
       </c>
       <c r="C121" s="28" t="n">
@@ -4256,25 +4857,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E121" s="28" t="inlineStr">
+      <c r="E121" s="37" t="inlineStr">
+        <is>
+          <t>This might be the find of the year.</t>
+        </is>
+      </c>
+      <c r="F121" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F121" s="28" t="inlineStr">
+      <c r="G121" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G121" s="31" t="inlineStr"/>
-      <c r="H121" s="30" t="n"/>
+      <c r="H121" s="31" t="inlineStr"/>
+      <c r="I121" s="30" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="28" t="n">
         <v>42</v>
       </c>
       <c r="B122" s="29">
-        <f>IF($E$3="","",$E$3+A122-1)</f>
+        <f>IF($B$3="","",$B$3+A122-1)</f>
         <v/>
       </c>
       <c r="C122" s="28" t="n">
@@ -4285,25 +4891,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E122" s="28" t="inlineStr">
+      <c r="E122" s="37" t="inlineStr">
+        <is>
+          <t>Before and after, no filter.</t>
+        </is>
+      </c>
+      <c r="F122" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F122" s="28" t="inlineStr">
+      <c r="G122" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G122" s="31" t="inlineStr"/>
-      <c r="H122" s="30" t="n"/>
+      <c r="H122" s="31" t="inlineStr"/>
+      <c r="I122" s="30" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="24" t="n">
         <v>42</v>
       </c>
       <c r="B123" s="25">
-        <f>IF($E$3="","",$E$3+A123-1)</f>
+        <f>IF($B$3="","",$B$3+A123-1)</f>
         <v/>
       </c>
       <c r="C123" s="24" t="n">
@@ -4314,25 +4925,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E123" s="24" t="inlineStr">
+      <c r="E123" s="36" t="inlineStr">
+        <is>
+          <t>The rain myth, settled today.</t>
+        </is>
+      </c>
+      <c r="F123" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F123" s="24" t="inlineStr">
+      <c r="G123" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G123" s="27" t="inlineStr"/>
-      <c r="H123" s="26" t="n"/>
+      <c r="H123" s="27" t="inlineStr"/>
+      <c r="I123" s="26" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="24" t="n">
         <v>42</v>
       </c>
       <c r="B124" s="25">
-        <f>IF($E$3="","",$E$3+A124-1)</f>
+        <f>IF($B$3="","",$B$3+A124-1)</f>
         <v/>
       </c>
       <c r="C124" s="24" t="n">
@@ -4343,20 +4959,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E124" s="24" t="inlineStr">
+      <c r="E124" s="36" t="inlineStr">
+        <is>
+          <t>Everyone said this ground was worked out.</t>
+        </is>
+      </c>
+      <c r="F124" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F124" s="24" t="inlineStr">
+      <c r="G124" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G124" s="27" t="inlineStr"/>
-      <c r="H124" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H124" s="27" t="inlineStr"/>
+      <c r="I124" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4986,7 @@
         <v>43</v>
       </c>
       <c r="B125" s="29">
-        <f>IF($E$3="","",$E$3+A125-1)</f>
+        <f>IF($B$3="","",$B$3+A125-1)</f>
         <v/>
       </c>
       <c r="C125" s="28" t="n">
@@ -4376,25 +4997,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E125" s="28" t="inlineStr">
+      <c r="E125" s="37" t="inlineStr">
+        <is>
+          <t>He nearly threw it back.</t>
+        </is>
+      </c>
+      <c r="F125" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F125" s="28" t="inlineStr">
+      <c r="G125" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G125" s="31" t="inlineStr"/>
-      <c r="H125" s="30" t="n"/>
+      <c r="H125" s="31" t="inlineStr"/>
+      <c r="I125" s="30" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="24" t="n">
         <v>43</v>
       </c>
       <c r="B126" s="25">
-        <f>IF($E$3="","",$E$3+A126-1)</f>
+        <f>IF($B$3="","",$B$3+A126-1)</f>
         <v/>
       </c>
       <c r="C126" s="24" t="n">
@@ -4405,25 +5031,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E126" s="24" t="inlineStr">
+      <c r="E126" s="36" t="inlineStr">
+        <is>
+          <t>The signal was screaming.</t>
+        </is>
+      </c>
+      <c r="F126" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F126" s="24" t="inlineStr">
+      <c r="G126" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G126" s="27" t="inlineStr"/>
-      <c r="H126" s="26" t="n"/>
+      <c r="H126" s="27" t="inlineStr"/>
+      <c r="I126" s="26" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="24" t="n">
         <v>43</v>
       </c>
       <c r="B127" s="25">
-        <f>IF($E$3="","",$E$3+A127-1)</f>
+        <f>IF($B$3="","",$B$3+A127-1)</f>
         <v/>
       </c>
       <c r="C127" s="24" t="n">
@@ -4434,25 +5065,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E127" s="24" t="inlineStr">
+      <c r="E127" s="36" t="inlineStr">
+        <is>
+          <t>The machine drew this before I touched a shovel.</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F127" s="24" t="inlineStr">
+      <c r="G127" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G127" s="27" t="inlineStr"/>
-      <c r="H127" s="26" t="n"/>
+      <c r="H127" s="27" t="inlineStr"/>
+      <c r="I127" s="26" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="28" t="n">
         <v>43</v>
       </c>
       <c r="B128" s="29">
-        <f>IF($E$3="","",$E$3+A128-1)</f>
+        <f>IF($B$3="","",$B$3+A128-1)</f>
         <v/>
       </c>
       <c r="C128" s="28" t="n">
@@ -4463,25 +5099,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E128" s="28" t="inlineStr">
+      <c r="E128" s="37" t="inlineStr">
+        <is>
+          <t>The first shine is the best part.</t>
+        </is>
+      </c>
+      <c r="F128" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F128" s="28" t="inlineStr">
+      <c r="G128" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G128" s="31" t="inlineStr"/>
-      <c r="H128" s="30" t="n"/>
+      <c r="H128" s="31" t="inlineStr"/>
+      <c r="I128" s="30" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="24" t="n">
         <v>44</v>
       </c>
       <c r="B129" s="25">
-        <f>IF($E$3="","",$E$3+A129-1)</f>
+        <f>IF($B$3="","",$B$3+A129-1)</f>
         <v/>
       </c>
       <c r="C129" s="24" t="n">
@@ -4492,25 +5133,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E129" s="24" t="inlineStr">
+      <c r="E129" s="36" t="inlineStr">
+        <is>
+          <t>Whatever this is, it's deep.</t>
+        </is>
+      </c>
+      <c r="F129" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F129" s="24" t="inlineStr">
+      <c r="G129" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G129" s="27" t="inlineStr"/>
-      <c r="H129" s="26" t="n"/>
+      <c r="H129" s="27" t="inlineStr"/>
+      <c r="I129" s="26" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="24" t="n">
         <v>44</v>
       </c>
       <c r="B130" s="25">
-        <f>IF($E$3="","",$E$3+A130-1)</f>
+        <f>IF($B$3="","",$B$3+A130-1)</f>
         <v/>
       </c>
       <c r="C130" s="24" t="n">
@@ -4521,25 +5167,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E130" s="24" t="inlineStr">
+      <c r="E130" s="36" t="inlineStr">
+        <is>
+          <t>Scan first, dig second. Here's why.</t>
+        </is>
+      </c>
+      <c r="F130" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F130" s="24" t="inlineStr">
+      <c r="G130" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G130" s="27" t="inlineStr"/>
-      <c r="H130" s="26" t="n"/>
+      <c r="H130" s="27" t="inlineStr"/>
+      <c r="I130" s="26" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="24" t="n">
         <v>44</v>
       </c>
       <c r="B131" s="25">
-        <f>IF($E$3="","",$E$3+A131-1)</f>
+        <f>IF($B$3="","",$B$3+A131-1)</f>
         <v/>
       </c>
       <c r="C131" s="24" t="n">
@@ -4550,20 +5201,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E131" s="24" t="inlineStr">
+      <c r="E131" s="36" t="inlineStr">
+        <is>
+          <t>The pan doesn't lie.</t>
+        </is>
+      </c>
+      <c r="F131" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F131" s="24" t="inlineStr">
+      <c r="G131" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G131" s="27" t="inlineStr"/>
-      <c r="H131" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H131" s="27" t="inlineStr"/>
+      <c r="I131" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -4572,7 +5228,7 @@
         <v>44</v>
       </c>
       <c r="B132" s="25">
-        <f>IF($E$3="","",$E$3+A132-1)</f>
+        <f>IF($B$3="","",$B$3+A132-1)</f>
         <v/>
       </c>
       <c r="C132" s="24" t="n">
@@ -4583,25 +5239,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E132" s="24" t="inlineStr">
+      <c r="E132" s="36" t="inlineStr">
+        <is>
+          <t>Grid's marked. Your move.</t>
+        </is>
+      </c>
+      <c r="F132" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F132" s="24" t="inlineStr">
+      <c r="G132" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G132" s="27" t="inlineStr"/>
-      <c r="H132" s="26" t="n"/>
+      <c r="H132" s="27" t="inlineStr"/>
+      <c r="I132" s="26" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="24" t="n">
         <v>45</v>
       </c>
       <c r="B133" s="25">
-        <f>IF($E$3="","",$E$3+A133-1)</f>
+        <f>IF($B$3="","",$B$3+A133-1)</f>
         <v/>
       </c>
       <c r="C133" s="24" t="n">
@@ -4612,25 +5273,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E133" s="24" t="inlineStr">
+      <c r="E133" s="36" t="inlineStr">
+        <is>
+          <t>I've never dug one this clean.</t>
+        </is>
+      </c>
+      <c r="F133" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F133" s="24" t="inlineStr">
+      <c r="G133" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G133" s="27" t="inlineStr"/>
-      <c r="H133" s="26" t="n"/>
+      <c r="H133" s="27" t="inlineStr"/>
+      <c r="I133" s="26" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="24" t="n">
         <v>45</v>
       </c>
       <c r="B134" s="25">
-        <f>IF($E$3="","",$E$3+A134-1)</f>
+        <f>IF($B$3="","",$B$3+A134-1)</f>
         <v/>
       </c>
       <c r="C134" s="24" t="n">
@@ -4641,25 +5307,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E134" s="24" t="inlineStr">
+      <c r="E134" s="36" t="inlineStr">
+        <is>
+          <t>Iron or silver? Listen again.</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F134" s="24" t="inlineStr">
+      <c r="G134" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G134" s="27" t="inlineStr"/>
-      <c r="H134" s="26" t="n"/>
+      <c r="H134" s="27" t="inlineStr"/>
+      <c r="I134" s="26" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="24" t="n">
         <v>45</v>
       </c>
       <c r="B135" s="25">
-        <f>IF($E$3="","",$E$3+A135-1)</f>
+        <f>IF($B$3="","",$B$3+A135-1)</f>
         <v/>
       </c>
       <c r="C135" s="24" t="n">
@@ -4670,25 +5341,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E135" s="24" t="inlineStr">
+      <c r="E135" s="36" t="inlineStr">
+        <is>
+          <t>Sixty minutes. Let's see what this sand is hiding.</t>
+        </is>
+      </c>
+      <c r="F135" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F135" s="24" t="inlineStr">
+      <c r="G135" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G135" s="27" t="inlineStr"/>
-      <c r="H135" s="26" t="n"/>
+      <c r="H135" s="27" t="inlineStr"/>
+      <c r="I135" s="26" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="24" t="n">
         <v>45</v>
       </c>
       <c r="B136" s="25">
-        <f>IF($E$3="","",$E$3+A136-1)</f>
+        <f>IF($B$3="","",$B$3+A136-1)</f>
         <v/>
       </c>
       <c r="C136" s="24" t="n">
@@ -4699,20 +5375,25 @@
           <t>05 Ring Recovery</t>
         </is>
       </c>
-      <c r="E136" s="24" t="inlineStr">
+      <c r="E136" s="36" t="inlineStr">
+        <is>
+          <t>He proposed with it. Then the tide took it.</t>
+        </is>
+      </c>
+      <c r="F136" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F136" s="24" t="inlineStr">
+      <c r="G136" s="24" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="G136" s="27" t="inlineStr"/>
-      <c r="H136" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H136" s="27" t="inlineStr"/>
+      <c r="I136" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -4721,7 +5402,7 @@
         <v>46</v>
       </c>
       <c r="B137" s="25">
-        <f>IF($E$3="","",$E$3+A137-1)</f>
+        <f>IF($B$3="","",$B$3+A137-1)</f>
         <v/>
       </c>
       <c r="C137" s="24" t="n">
@@ -4732,25 +5413,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E137" s="24" t="inlineStr">
+      <c r="E137" s="36" t="inlineStr">
+        <is>
+          <t>That flutter means it's sitting on edge.</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F137" s="24" t="inlineStr">
+      <c r="G137" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G137" s="27" t="inlineStr"/>
-      <c r="H137" s="26" t="n"/>
+      <c r="H137" s="27" t="inlineStr"/>
+      <c r="I137" s="26" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="24" t="n">
         <v>46</v>
       </c>
       <c r="B138" s="25">
-        <f>IF($E$3="","",$E$3+A138-1)</f>
+        <f>IF($B$3="","",$B$3+A138-1)</f>
         <v/>
       </c>
       <c r="C138" s="24" t="n">
@@ -4761,25 +5447,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E138" s="24" t="inlineStr">
+      <c r="E138" s="36" t="inlineStr">
+        <is>
+          <t>This is why beginners quit. Watch.</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F138" s="24" t="inlineStr">
+      <c r="G138" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G138" s="27" t="inlineStr"/>
-      <c r="H138" s="26" t="n"/>
+      <c r="H138" s="27" t="inlineStr"/>
+      <c r="I138" s="26" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="24" t="n">
         <v>46</v>
       </c>
       <c r="B139" s="25">
-        <f>IF($E$3="","",$E$3+A139-1)</f>
+        <f>IF($B$3="","",$B$3+A139-1)</f>
         <v/>
       </c>
       <c r="C139" s="24" t="n">
@@ -4790,20 +5481,25 @@
           <t>05 Ring Recovery</t>
         </is>
       </c>
-      <c r="E139" s="24" t="inlineStr">
+      <c r="E139" s="36" t="inlineStr">
+        <is>
+          <t>Forty minutes of searching for something this small.</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F139" s="24" t="inlineStr">
+      <c r="G139" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G139" s="27" t="inlineStr"/>
-      <c r="H139" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H139" s="27" t="inlineStr"/>
+      <c r="I139" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -4812,7 +5508,7 @@
         <v>46</v>
       </c>
       <c r="B140" s="25">
-        <f>IF($E$3="","",$E$3+A140-1)</f>
+        <f>IF($B$3="","",$B$3+A140-1)</f>
         <v/>
       </c>
       <c r="C140" s="24" t="n">
@@ -4823,25 +5519,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E140" s="24" t="inlineStr">
+      <c r="E140" s="36" t="inlineStr">
+        <is>
+          <t>Identical conditions, honest result.</t>
+        </is>
+      </c>
+      <c r="F140" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F140" s="24" t="inlineStr">
+      <c r="G140" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G140" s="27" t="inlineStr"/>
-      <c r="H140" s="26" t="n"/>
+      <c r="H140" s="27" t="inlineStr"/>
+      <c r="I140" s="26" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="28" t="n">
         <v>47</v>
       </c>
       <c r="B141" s="29">
-        <f>IF($E$3="","",$E$3+A141-1)</f>
+        <f>IF($B$3="","",$B$3+A141-1)</f>
         <v/>
       </c>
       <c r="C141" s="28" t="n">
@@ -4852,25 +5553,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E141" s="28" t="inlineStr">
+      <c r="E141" s="37" t="inlineStr">
+        <is>
+          <t>Green to gold in three minutes.</t>
+        </is>
+      </c>
+      <c r="F141" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F141" s="28" t="inlineStr">
+      <c r="G141" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G141" s="31" t="inlineStr"/>
-      <c r="H141" s="30" t="n"/>
+      <c r="H141" s="31" t="inlineStr"/>
+      <c r="I141" s="30" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="24" t="n">
         <v>47</v>
       </c>
       <c r="B142" s="25">
-        <f>IF($E$3="","",$E$3+A142-1)</f>
+        <f>IF($B$3="","",$B$3+A142-1)</f>
         <v/>
       </c>
       <c r="C142" s="24" t="n">
@@ -4881,20 +5587,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E142" s="24" t="inlineStr">
+      <c r="E142" s="36" t="inlineStr">
+        <is>
+          <t>Six hours for this, and worth every one.</t>
+        </is>
+      </c>
+      <c r="F142" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F142" s="24" t="inlineStr">
+      <c r="G142" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G142" s="27" t="inlineStr"/>
-      <c r="H142" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H142" s="27" t="inlineStr"/>
+      <c r="I142" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -4903,7 +5614,7 @@
         <v>47</v>
       </c>
       <c r="B143" s="29">
-        <f>IF($E$3="","",$E$3+A143-1)</f>
+        <f>IF($B$3="","",$B$3+A143-1)</f>
         <v/>
       </c>
       <c r="C143" s="28" t="n">
@@ -4914,25 +5625,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E143" s="28" t="inlineStr">
+      <c r="E143" s="37" t="inlineStr">
+        <is>
+          <t>Watch his face when he realises.</t>
+        </is>
+      </c>
+      <c r="F143" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F143" s="28" t="inlineStr">
+      <c r="G143" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G143" s="31" t="inlineStr"/>
-      <c r="H143" s="30" t="n"/>
+      <c r="H143" s="31" t="inlineStr"/>
+      <c r="I143" s="30" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="24" t="n">
         <v>47</v>
       </c>
       <c r="B144" s="25">
-        <f>IF($E$3="","",$E$3+A144-1)</f>
+        <f>IF($B$3="","",$B$3+A144-1)</f>
         <v/>
       </c>
       <c r="C144" s="24" t="n">
@@ -4943,25 +5659,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E144" s="24" t="inlineStr">
+      <c r="E144" s="36" t="inlineStr">
+        <is>
+          <t>I tested both so you don't have to.</t>
+        </is>
+      </c>
+      <c r="F144" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F144" s="24" t="inlineStr">
+      <c r="G144" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G144" s="27" t="inlineStr"/>
-      <c r="H144" s="26" t="n"/>
+      <c r="H144" s="27" t="inlineStr"/>
+      <c r="I144" s="26" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="28" t="n">
         <v>48</v>
       </c>
       <c r="B145" s="29">
-        <f>IF($E$3="","",$E$3+A145-1)</f>
+        <f>IF($B$3="","",$B$3+A145-1)</f>
         <v/>
       </c>
       <c r="C145" s="28" t="n">
@@ -4972,25 +5693,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E145" s="28" t="inlineStr">
+      <c r="E145" s="37" t="inlineStr">
+        <is>
+          <t>Sixty years of dirt. Watch.</t>
+        </is>
+      </c>
+      <c r="F145" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F145" s="28" t="inlineStr">
+      <c r="G145" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G145" s="31" t="inlineStr"/>
-      <c r="H145" s="30" t="n"/>
+      <c r="H145" s="31" t="inlineStr"/>
+      <c r="I145" s="30" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="24" t="n">
         <v>48</v>
       </c>
       <c r="B146" s="25">
-        <f>IF($E$3="","",$E$3+A146-1)</f>
+        <f>IF($B$3="","",$B$3+A146-1)</f>
         <v/>
       </c>
       <c r="C146" s="24" t="n">
@@ -5001,25 +5727,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E146" s="24" t="inlineStr">
+      <c r="E146" s="36" t="inlineStr">
+        <is>
+          <t>One hour, one detector, no cherry-picking.</t>
+        </is>
+      </c>
+      <c r="F146" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F146" s="24" t="inlineStr">
+      <c r="G146" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G146" s="27" t="inlineStr"/>
-      <c r="H146" s="26" t="n"/>
+      <c r="H146" s="27" t="inlineStr"/>
+      <c r="I146" s="26" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="24" t="n">
         <v>48</v>
       </c>
       <c r="B147" s="25">
-        <f>IF($E$3="","",$E$3+A147-1)</f>
+        <f>IF($B$3="","",$B$3+A147-1)</f>
         <v/>
       </c>
       <c r="C147" s="24" t="n">
@@ -5030,25 +5761,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E147" s="24" t="inlineStr">
+      <c r="E147" s="36" t="inlineStr">
+        <is>
+          <t>Something big is under here, and it isn't a pipe.</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F147" s="24" t="inlineStr">
+      <c r="G147" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G147" s="27" t="inlineStr"/>
-      <c r="H147" s="26" t="n"/>
+      <c r="H147" s="27" t="inlineStr"/>
+      <c r="I147" s="26" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="24" t="n">
         <v>48</v>
       </c>
       <c r="B148" s="25">
-        <f>IF($E$3="","",$E$3+A148-1)</f>
+        <f>IF($B$3="","",$B$3+A148-1)</f>
         <v/>
       </c>
       <c r="C148" s="24" t="n">
@@ -5059,25 +5795,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E148" s="24" t="inlineStr">
+      <c r="E148" s="36" t="inlineStr">
+        <is>
+          <t>Most comments wins. I dig at dawn.</t>
+        </is>
+      </c>
+      <c r="F148" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F148" s="24" t="inlineStr">
+      <c r="G148" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G148" s="27" t="inlineStr"/>
-      <c r="H148" s="26" t="n"/>
+      <c r="H148" s="27" t="inlineStr"/>
+      <c r="I148" s="26" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="24" t="n">
         <v>49</v>
       </c>
       <c r="B149" s="25">
-        <f>IF($E$3="","",$E$3+A149-1)</f>
+        <f>IF($B$3="","",$B$3+A149-1)</f>
         <v/>
       </c>
       <c r="C149" s="24" t="n">
@@ -5088,25 +5829,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E149" s="24" t="inlineStr">
+      <c r="E149" s="36" t="inlineStr">
+        <is>
+          <t>Everything I find in an hour. Good and bad.</t>
+        </is>
+      </c>
+      <c r="F149" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F149" s="24" t="inlineStr">
+      <c r="G149" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G149" s="27" t="inlineStr"/>
-      <c r="H149" s="26" t="n"/>
+      <c r="H149" s="27" t="inlineStr"/>
+      <c r="I149" s="26" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="28" t="n">
         <v>49</v>
       </c>
       <c r="B150" s="29">
-        <f>IF($E$3="","",$E$3+A150-1)</f>
+        <f>IF($B$3="","",$B$3+A150-1)</f>
         <v/>
       </c>
       <c r="C150" s="28" t="n">
@@ -5117,25 +5863,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E150" s="28" t="inlineStr">
+      <c r="E150" s="37" t="inlineStr">
+        <is>
+          <t>You will not believe what's under this.</t>
+        </is>
+      </c>
+      <c r="F150" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F150" s="28" t="inlineStr">
+      <c r="G150" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G150" s="31" t="inlineStr"/>
-      <c r="H150" s="30" t="n"/>
+      <c r="H150" s="31" t="inlineStr"/>
+      <c r="I150" s="30" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="28" t="n">
         <v>49</v>
       </c>
       <c r="B151" s="29">
-        <f>IF($E$3="","",$E$3+A151-1)</f>
+        <f>IF($B$3="","",$B$3+A151-1)</f>
         <v/>
       </c>
       <c r="C151" s="28" t="n">
@@ -5146,25 +5897,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E151" s="28" t="inlineStr">
+      <c r="E151" s="37" t="inlineStr">
+        <is>
+          <t>I've been sent a hundred of these. This one's different.</t>
+        </is>
+      </c>
+      <c r="F151" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F151" s="28" t="inlineStr">
+      <c r="G151" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G151" s="31" t="inlineStr"/>
-      <c r="H151" s="30" t="n"/>
+      <c r="H151" s="31" t="inlineStr"/>
+      <c r="I151" s="30" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="24" t="n">
         <v>49</v>
       </c>
       <c r="B152" s="25">
-        <f>IF($E$3="","",$E$3+A152-1)</f>
+        <f>IF($B$3="","",$B$3+A152-1)</f>
         <v/>
       </c>
       <c r="C152" s="24" t="n">
@@ -5175,25 +5931,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E152" s="24" t="inlineStr">
+      <c r="E152" s="36" t="inlineStr">
+        <is>
+          <t>Everyone's detector missed this.</t>
+        </is>
+      </c>
+      <c r="F152" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F152" s="24" t="inlineStr">
+      <c r="G152" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G152" s="27" t="inlineStr"/>
-      <c r="H152" s="26" t="n"/>
+      <c r="H152" s="27" t="inlineStr"/>
+      <c r="I152" s="26" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="28" t="n">
         <v>50</v>
       </c>
       <c r="B153" s="29">
-        <f>IF($E$3="","",$E$3+A153-1)</f>
+        <f>IF($B$3="","",$B$3+A153-1)</f>
         <v/>
       </c>
       <c r="C153" s="28" t="n">
@@ -5204,25 +5965,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E153" s="28" t="inlineStr">
+      <c r="E153" s="37" t="inlineStr">
+        <is>
+          <t>That is not what he thinks it is.</t>
+        </is>
+      </c>
+      <c r="F153" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F153" s="28" t="inlineStr">
+      <c r="G153" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G153" s="31" t="inlineStr"/>
-      <c r="H153" s="30" t="n"/>
+      <c r="H153" s="31" t="inlineStr"/>
+      <c r="I153" s="30" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="24" t="n">
         <v>50</v>
       </c>
       <c r="B154" s="25">
-        <f>IF($E$3="","",$E$3+A154-1)</f>
+        <f>IF($B$3="","",$B$3+A154-1)</f>
         <v/>
       </c>
       <c r="C154" s="24" t="n">
@@ -5233,25 +5999,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E154" s="24" t="inlineStr">
+      <c r="E154" s="36" t="inlineStr">
+        <is>
+          <t>Watch the dirt come off this.</t>
+        </is>
+      </c>
+      <c r="F154" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F154" s="24" t="inlineStr">
+      <c r="G154" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G154" s="27" t="inlineStr"/>
-      <c r="H154" s="26" t="n"/>
+      <c r="H154" s="27" t="inlineStr"/>
+      <c r="I154" s="26" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="24" t="n">
         <v>50</v>
       </c>
       <c r="B155" s="25">
-        <f>IF($E$3="","",$E$3+A155-1)</f>
+        <f>IF($B$3="","",$B$3+A155-1)</f>
         <v/>
       </c>
       <c r="C155" s="24" t="n">
@@ -5262,25 +6033,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E155" s="24" t="inlineStr">
+      <c r="E155" s="36" t="inlineStr">
+        <is>
+          <t>I scanned before I dug. Here's what it showed.</t>
+        </is>
+      </c>
+      <c r="F155" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F155" s="24" t="inlineStr">
+      <c r="G155" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G155" s="27" t="inlineStr"/>
-      <c r="H155" s="26" t="n"/>
+      <c r="H155" s="27" t="inlineStr"/>
+      <c r="I155" s="26" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="24" t="n">
         <v>50</v>
       </c>
       <c r="B156" s="25">
-        <f>IF($E$3="","",$E$3+A156-1)</f>
+        <f>IF($B$3="","",$B$3+A156-1)</f>
         <v/>
       </c>
       <c r="C156" s="24" t="n">
@@ -5291,25 +6067,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E156" s="24" t="inlineStr">
+      <c r="E156" s="36" t="inlineStr">
+        <is>
+          <t>An hour here after a storm. This should be good.</t>
+        </is>
+      </c>
+      <c r="F156" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F156" s="24" t="inlineStr">
+      <c r="G156" s="24" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="G156" s="27" t="inlineStr"/>
-      <c r="H156" s="26" t="n"/>
+      <c r="H156" s="27" t="inlineStr"/>
+      <c r="I156" s="26" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="24" t="n">
         <v>51</v>
       </c>
       <c r="B157" s="25">
-        <f>IF($E$3="","",$E$3+A157-1)</f>
+        <f>IF($B$3="","",$B$3+A157-1)</f>
         <v/>
       </c>
       <c r="C157" s="24" t="n">
@@ -5320,25 +6101,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E157" s="24" t="inlineStr">
+      <c r="E157" s="36" t="inlineStr">
+        <is>
+          <t>Bottle cap. Bottle cap. Bottle cap. Oh.</t>
+        </is>
+      </c>
+      <c r="F157" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F157" s="24" t="inlineStr">
+      <c r="G157" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G157" s="27" t="inlineStr"/>
-      <c r="H157" s="26" t="n"/>
+      <c r="H157" s="27" t="inlineStr"/>
+      <c r="I157" s="26" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="24" t="n">
         <v>51</v>
       </c>
       <c r="B158" s="25">
-        <f>IF($E$3="","",$E$3+A158-1)</f>
+        <f>IF($B$3="","",$B$3+A158-1)</f>
         <v/>
       </c>
       <c r="C158" s="24" t="n">
@@ -5349,25 +6135,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E158" s="24" t="inlineStr">
+      <c r="E158" s="36" t="inlineStr">
+        <is>
+          <t>Everybody repeats this. Nobody's tested it.</t>
+        </is>
+      </c>
+      <c r="F158" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F158" s="24" t="inlineStr">
+      <c r="G158" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G158" s="27" t="inlineStr"/>
-      <c r="H158" s="26" t="n"/>
+      <c r="H158" s="27" t="inlineStr"/>
+      <c r="I158" s="26" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="28" t="n">
         <v>51</v>
       </c>
       <c r="B159" s="29">
-        <f>IF($E$3="","",$E$3+A159-1)</f>
+        <f>IF($B$3="","",$B$3+A159-1)</f>
         <v/>
       </c>
       <c r="C159" s="28" t="n">
@@ -5378,25 +6169,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E159" s="28" t="inlineStr">
+      <c r="E159" s="37" t="inlineStr">
+        <is>
+          <t>No talking. Just cleaning.</t>
+        </is>
+      </c>
+      <c r="F159" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F159" s="28" t="inlineStr">
+      <c r="G159" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G159" s="31" t="inlineStr"/>
-      <c r="H159" s="30" t="n"/>
+      <c r="H159" s="31" t="inlineStr"/>
+      <c r="I159" s="30" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="24" t="n">
         <v>51</v>
       </c>
       <c r="B160" s="25">
-        <f>IF($E$3="","",$E$3+A160-1)</f>
+        <f>IF($B$3="","",$B$3+A160-1)</f>
         <v/>
       </c>
       <c r="C160" s="24" t="n">
@@ -5407,25 +6203,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E160" s="24" t="inlineStr">
+      <c r="E160" s="36" t="inlineStr">
+        <is>
+          <t>How much can one hour actually pay?</t>
+        </is>
+      </c>
+      <c r="F160" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F160" s="24" t="inlineStr">
+      <c r="G160" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G160" s="27" t="inlineStr"/>
-      <c r="H160" s="26" t="n"/>
+      <c r="H160" s="27" t="inlineStr"/>
+      <c r="I160" s="26" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="28" t="n">
         <v>52</v>
       </c>
       <c r="B161" s="29">
-        <f>IF($E$3="","",$E$3+A161-1)</f>
+        <f>IF($B$3="","",$B$3+A161-1)</f>
         <v/>
       </c>
       <c r="C161" s="28" t="n">
@@ -5436,25 +6237,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E161" s="28" t="inlineStr">
+      <c r="E161" s="37" t="inlineStr">
+        <is>
+          <t>He has no idea what he just dug up.</t>
+        </is>
+      </c>
+      <c r="F161" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F161" s="28" t="inlineStr">
+      <c r="G161" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G161" s="31" t="inlineStr"/>
-      <c r="H161" s="30" t="n"/>
+      <c r="H161" s="31" t="inlineStr"/>
+      <c r="I161" s="30" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="28" t="n">
         <v>52</v>
       </c>
       <c r="B162" s="29">
-        <f>IF($E$3="","",$E$3+A162-1)</f>
+        <f>IF($B$3="","",$B$3+A162-1)</f>
         <v/>
       </c>
       <c r="C162" s="28" t="n">
@@ -5465,25 +6271,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E162" s="28" t="inlineStr">
+      <c r="E162" s="37" t="inlineStr">
+        <is>
+          <t>Give it thirty seconds.</t>
+        </is>
+      </c>
+      <c r="F162" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F162" s="28" t="inlineStr">
+      <c r="G162" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G162" s="31" t="inlineStr"/>
-      <c r="H162" s="30" t="n"/>
+      <c r="H162" s="31" t="inlineStr"/>
+      <c r="I162" s="30" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="24" t="n">
         <v>52</v>
       </c>
       <c r="B163" s="25">
-        <f>IF($E$3="","",$E$3+A163-1)</f>
+        <f>IF($B$3="","",$B$3+A163-1)</f>
         <v/>
       </c>
       <c r="C163" s="24" t="n">
@@ -5494,25 +6305,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E163" s="24" t="inlineStr">
+      <c r="E163" s="36" t="inlineStr">
+        <is>
+          <t>Comment a number. I'm digging whichever square wins.</t>
+        </is>
+      </c>
+      <c r="F163" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F163" s="24" t="inlineStr">
+      <c r="G163" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G163" s="27" t="inlineStr"/>
-      <c r="H163" s="26" t="n"/>
+      <c r="H163" s="27" t="inlineStr"/>
+      <c r="I163" s="26" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="24" t="n">
         <v>52</v>
       </c>
       <c r="B164" s="25">
-        <f>IF($E$3="","",$E$3+A164-1)</f>
+        <f>IF($B$3="","",$B$3+A164-1)</f>
         <v/>
       </c>
       <c r="C164" s="24" t="n">
@@ -5523,20 +6339,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E164" s="24" t="inlineStr">
+      <c r="E164" s="36" t="inlineStr">
+        <is>
+          <t>That colour in the scoop. You know the one.</t>
+        </is>
+      </c>
+      <c r="F164" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F164" s="24" t="inlineStr">
+      <c r="G164" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G164" s="27" t="inlineStr"/>
-      <c r="H164" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H164" s="27" t="inlineStr"/>
+      <c r="I164" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -5545,7 +6366,7 @@
         <v>53</v>
       </c>
       <c r="B165" s="29">
-        <f>IF($E$3="","",$E$3+A165-1)</f>
+        <f>IF($B$3="","",$B$3+A165-1)</f>
         <v/>
       </c>
       <c r="C165" s="28" t="n">
@@ -5556,25 +6377,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E165" s="28" t="inlineStr">
+      <c r="E165" s="37" t="inlineStr">
+        <is>
+          <t>She thinks that's junk. It isn't.</t>
+        </is>
+      </c>
+      <c r="F165" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F165" s="28" t="inlineStr">
+      <c r="G165" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G165" s="31" t="inlineStr"/>
-      <c r="H165" s="30" t="n"/>
+      <c r="H165" s="31" t="inlineStr"/>
+      <c r="I165" s="30" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="24" t="n">
         <v>53</v>
       </c>
       <c r="B166" s="25">
-        <f>IF($E$3="","",$E$3+A166-1)</f>
+        <f>IF($B$3="","",$B$3+A166-1)</f>
         <v/>
       </c>
       <c r="C166" s="24" t="n">
@@ -5585,25 +6411,30 @@
           <t>03 You Pick the Spot</t>
         </is>
       </c>
-      <c r="E166" s="24" t="inlineStr">
+      <c r="E166" s="36" t="inlineStr">
+        <is>
+          <t>Nine squares. You choose, I dig.</t>
+        </is>
+      </c>
+      <c r="F166" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F166" s="24" t="inlineStr">
+      <c r="G166" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G166" s="27" t="inlineStr"/>
-      <c r="H166" s="26" t="n"/>
+      <c r="H166" s="27" t="inlineStr"/>
+      <c r="I166" s="26" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="28" t="n">
         <v>53</v>
       </c>
       <c r="B167" s="29">
-        <f>IF($E$3="","",$E$3+A167-1)</f>
+        <f>IF($B$3="","",$B$3+A167-1)</f>
         <v/>
       </c>
       <c r="C167" s="28" t="n">
@@ -5614,25 +6445,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E167" s="28" t="inlineStr">
+      <c r="E167" s="37" t="inlineStr">
+        <is>
+          <t>This came out of the ground looking like a rock.</t>
+        </is>
+      </c>
+      <c r="F167" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F167" s="28" t="inlineStr">
+      <c r="G167" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G167" s="31" t="inlineStr"/>
-      <c r="H167" s="30" t="n"/>
+      <c r="H167" s="31" t="inlineStr"/>
+      <c r="I167" s="30" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="24" t="n">
         <v>53</v>
       </c>
       <c r="B168" s="25">
-        <f>IF($E$3="","",$E$3+A168-1)</f>
+        <f>IF($B$3="","",$B$3+A168-1)</f>
         <v/>
       </c>
       <c r="C168" s="24" t="n">
@@ -5643,25 +6479,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E168" s="24" t="inlineStr">
+      <c r="E168" s="36" t="inlineStr">
+        <is>
+          <t>One sound, two very different outcomes.</t>
+        </is>
+      </c>
+      <c r="F168" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F168" s="24" t="inlineStr">
+      <c r="G168" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G168" s="27" t="inlineStr"/>
-      <c r="H168" s="26" t="n"/>
+      <c r="H168" s="27" t="inlineStr"/>
+      <c r="I168" s="26" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="28" t="n">
         <v>54</v>
       </c>
       <c r="B169" s="29">
-        <f>IF($E$3="","",$E$3+A169-1)</f>
+        <f>IF($B$3="","",$B$3+A169-1)</f>
         <v/>
       </c>
       <c r="C169" s="28" t="n">
@@ -5672,25 +6513,30 @@
           <t>08 ASMR Restoration</t>
         </is>
       </c>
-      <c r="E169" s="28" t="inlineStr">
+      <c r="E169" s="37" t="inlineStr">
+        <is>
+          <t>Before and after, no filter.</t>
+        </is>
+      </c>
+      <c r="F169" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F169" s="28" t="inlineStr">
+      <c r="G169" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G169" s="31" t="inlineStr"/>
-      <c r="H169" s="30" t="n"/>
+      <c r="H169" s="31" t="inlineStr"/>
+      <c r="I169" s="30" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="24" t="n">
         <v>54</v>
       </c>
       <c r="B170" s="25">
-        <f>IF($E$3="","",$E$3+A170-1)</f>
+        <f>IF($B$3="","",$B$3+A170-1)</f>
         <v/>
       </c>
       <c r="C170" s="24" t="n">
@@ -5701,25 +6547,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E170" s="24" t="inlineStr">
+      <c r="E170" s="36" t="inlineStr">
+        <is>
+          <t>This $300 detector says there's nothing here.</t>
+        </is>
+      </c>
+      <c r="F170" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F170" s="24" t="inlineStr">
+      <c r="G170" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G170" s="27" t="inlineStr"/>
-      <c r="H170" s="26" t="n"/>
+      <c r="H170" s="27" t="inlineStr"/>
+      <c r="I170" s="26" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="24" t="n">
         <v>54</v>
       </c>
       <c r="B171" s="25">
-        <f>IF($E$3="","",$E$3+A171-1)</f>
+        <f>IF($B$3="","",$B$3+A171-1)</f>
         <v/>
       </c>
       <c r="C171" s="24" t="n">
@@ -5730,25 +6581,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E171" s="24" t="inlineStr">
+      <c r="E171" s="36" t="inlineStr">
+        <is>
+          <t>This ground's been hunted a thousand times.</t>
+        </is>
+      </c>
+      <c r="F171" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F171" s="24" t="inlineStr">
+      <c r="G171" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G171" s="27" t="inlineStr"/>
-      <c r="H171" s="26" t="n"/>
+      <c r="H171" s="27" t="inlineStr"/>
+      <c r="I171" s="26" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="24" t="n">
         <v>54</v>
       </c>
       <c r="B172" s="25">
-        <f>IF($E$3="","",$E$3+A172-1)</f>
+        <f>IF($B$3="","",$B$3+A172-1)</f>
         <v/>
       </c>
       <c r="C172" s="24" t="n">
@@ -5759,20 +6615,25 @@
           <t>07 Gold Hunt</t>
         </is>
       </c>
-      <c r="E172" s="24" t="inlineStr">
+      <c r="E172" s="36" t="inlineStr">
+        <is>
+          <t>If this is what I think it is...</t>
+        </is>
+      </c>
+      <c r="F172" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F172" s="24" t="inlineStr">
+      <c r="G172" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G172" s="27" t="inlineStr"/>
-      <c r="H172" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H172" s="27" t="inlineStr"/>
+      <c r="I172" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -5781,7 +6642,7 @@
         <v>55</v>
       </c>
       <c r="B173" s="25">
-        <f>IF($E$3="","",$E$3+A173-1)</f>
+        <f>IF($B$3="","",$B$3+A173-1)</f>
         <v/>
       </c>
       <c r="C173" s="24" t="n">
@@ -5792,25 +6653,30 @@
           <t>06 The Hour Haul</t>
         </is>
       </c>
-      <c r="E173" s="24" t="inlineStr">
+      <c r="E173" s="36" t="inlineStr">
+        <is>
+          <t>Timer's on. Let's go.</t>
+        </is>
+      </c>
+      <c r="F173" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F173" s="24" t="inlineStr">
+      <c r="G173" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G173" s="27" t="inlineStr"/>
-      <c r="H173" s="26" t="n"/>
+      <c r="H173" s="27" t="inlineStr"/>
+      <c r="I173" s="26" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="28" t="n">
         <v>55</v>
       </c>
       <c r="B174" s="29">
-        <f>IF($E$3="","",$E$3+A174-1)</f>
+        <f>IF($B$3="","",$B$3+A174-1)</f>
         <v/>
       </c>
       <c r="C174" s="28" t="n">
@@ -5821,25 +6687,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E174" s="28" t="inlineStr">
+      <c r="E174" s="37" t="inlineStr">
+        <is>
+          <t>This might be the find of the year.</t>
+        </is>
+      </c>
+      <c r="F174" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F174" s="28" t="inlineStr">
+      <c r="G174" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G174" s="31" t="inlineStr"/>
-      <c r="H174" s="30" t="n"/>
+      <c r="H174" s="31" t="inlineStr"/>
+      <c r="I174" s="30" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="24" t="n">
         <v>55</v>
       </c>
       <c r="B175" s="25">
-        <f>IF($E$3="","",$E$3+A175-1)</f>
+        <f>IF($B$3="","",$B$3+A175-1)</f>
         <v/>
       </c>
       <c r="C175" s="24" t="n">
@@ -5850,25 +6721,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E175" s="24" t="inlineStr">
+      <c r="E175" s="36" t="inlineStr">
+        <is>
+          <t>Same spot, same target. One of these finds it.</t>
+        </is>
+      </c>
+      <c r="F175" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F175" s="24" t="inlineStr">
+      <c r="G175" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G175" s="27" t="inlineStr"/>
-      <c r="H175" s="26" t="n"/>
+      <c r="H175" s="27" t="inlineStr"/>
+      <c r="I175" s="26" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="24" t="n">
         <v>55</v>
       </c>
       <c r="B176" s="25">
-        <f>IF($E$3="","",$E$3+A176-1)</f>
+        <f>IF($B$3="","",$B$3+A176-1)</f>
         <v/>
       </c>
       <c r="C176" s="24" t="n">
@@ -5879,20 +6755,25 @@
           <t>05 Ring Recovery</t>
         </is>
       </c>
-      <c r="E176" s="24" t="inlineStr">
+      <c r="E176" s="36" t="inlineStr">
+        <is>
+          <t>She'd already given up on it.</t>
+        </is>
+      </c>
+      <c r="F176" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F176" s="24" t="inlineStr">
+      <c r="G176" s="24" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="G176" s="27" t="inlineStr"/>
-      <c r="H176" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H176" s="27" t="inlineStr"/>
+      <c r="I176" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -5901,7 +6782,7 @@
         <v>56</v>
       </c>
       <c r="B177" s="25">
-        <f>IF($E$3="","",$E$3+A177-1)</f>
+        <f>IF($B$3="","",$B$3+A177-1)</f>
         <v/>
       </c>
       <c r="C177" s="24" t="n">
@@ -5912,25 +6793,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E177" s="24" t="inlineStr">
+      <c r="E177" s="36" t="inlineStr">
+        <is>
+          <t>Learn this tone and you'll double your finds.</t>
+        </is>
+      </c>
+      <c r="F177" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F177" s="24" t="inlineStr">
+      <c r="G177" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G177" s="27" t="inlineStr"/>
-      <c r="H177" s="26" t="n"/>
+      <c r="H177" s="27" t="inlineStr"/>
+      <c r="I177" s="26" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="24" t="n">
         <v>56</v>
       </c>
       <c r="B178" s="25">
-        <f>IF($E$3="","",$E$3+A178-1)</f>
+        <f>IF($B$3="","",$B$3+A178-1)</f>
         <v/>
       </c>
       <c r="C178" s="24" t="n">
@@ -5941,25 +6827,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E178" s="24" t="inlineStr">
+      <c r="E178" s="36" t="inlineStr">
+        <is>
+          <t>That tone means it's silver.</t>
+        </is>
+      </c>
+      <c r="F178" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F178" s="24" t="inlineStr">
+      <c r="G178" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G178" s="27" t="inlineStr"/>
-      <c r="H178" s="26" t="n"/>
+      <c r="H178" s="27" t="inlineStr"/>
+      <c r="I178" s="26" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="24" t="n">
         <v>56</v>
       </c>
       <c r="B179" s="25">
-        <f>IF($E$3="","",$E$3+A179-1)</f>
+        <f>IF($B$3="","",$B$3+A179-1)</f>
         <v/>
       </c>
       <c r="C179" s="24" t="n">
@@ -5970,25 +6861,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E179" s="24" t="inlineStr">
+      <c r="E179" s="36" t="inlineStr">
+        <is>
+          <t>I hope I'm wrong about this one.</t>
+        </is>
+      </c>
+      <c r="F179" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F179" s="24" t="inlineStr">
+      <c r="G179" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G179" s="27" t="inlineStr"/>
-      <c r="H179" s="26" t="n"/>
+      <c r="H179" s="27" t="inlineStr"/>
+      <c r="I179" s="26" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="24" t="n">
         <v>56</v>
       </c>
       <c r="B180" s="25">
-        <f>IF($E$3="","",$E$3+A180-1)</f>
+        <f>IF($B$3="","",$B$3+A180-1)</f>
         <v/>
       </c>
       <c r="C180" s="24" t="n">
@@ -5999,25 +6895,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E180" s="24" t="inlineStr">
+      <c r="E180" s="36" t="inlineStr">
+        <is>
+          <t>I buried this at four feet. Let's see which one screams.</t>
+        </is>
+      </c>
+      <c r="F180" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F180" s="24" t="inlineStr">
+      <c r="G180" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G180" s="27" t="inlineStr"/>
-      <c r="H180" s="26" t="n"/>
+      <c r="H180" s="27" t="inlineStr"/>
+      <c r="I180" s="26" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="28" t="n">
         <v>57</v>
       </c>
       <c r="B181" s="29">
-        <f>IF($E$3="","",$E$3+A181-1)</f>
+        <f>IF($B$3="","",$B$3+A181-1)</f>
         <v/>
       </c>
       <c r="C181" s="28" t="n">
@@ -6028,25 +6929,30 @@
           <t>10 Detectorist Reacts</t>
         </is>
       </c>
-      <c r="E181" s="28" t="inlineStr">
+      <c r="E181" s="37" t="inlineStr">
+        <is>
+          <t>He nearly threw it back.</t>
+        </is>
+      </c>
+      <c r="F181" s="28" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F181" s="28" t="inlineStr">
+      <c r="G181" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G181" s="31" t="inlineStr"/>
-      <c r="H181" s="30" t="n"/>
+      <c r="H181" s="31" t="inlineStr"/>
+      <c r="I181" s="30" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="24" t="n">
         <v>57</v>
       </c>
       <c r="B182" s="25">
-        <f>IF($E$3="","",$E$3+A182-1)</f>
+        <f>IF($B$3="","",$B$3+A182-1)</f>
         <v/>
       </c>
       <c r="C182" s="24" t="n">
@@ -6057,25 +6963,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E182" s="24" t="inlineStr">
+      <c r="E182" s="36" t="inlineStr">
+        <is>
+          <t>I almost walked past this.</t>
+        </is>
+      </c>
+      <c r="F182" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F182" s="24" t="inlineStr">
+      <c r="G182" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G182" s="27" t="inlineStr"/>
-      <c r="H182" s="26" t="n"/>
+      <c r="H182" s="27" t="inlineStr"/>
+      <c r="I182" s="26" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="24" t="n">
         <v>57</v>
       </c>
       <c r="B183" s="25">
-        <f>IF($E$3="","",$E$3+A183-1)</f>
+        <f>IF($B$3="","",$B$3+A183-1)</f>
         <v/>
       </c>
       <c r="C183" s="24" t="n">
@@ -6086,25 +6997,30 @@
           <t>01 The Depth Duel</t>
         </is>
       </c>
-      <c r="E183" s="24" t="inlineStr">
+      <c r="E183" s="36" t="inlineStr">
+        <is>
+          <t>Your detector isn't broken. It's just shallow.</t>
+        </is>
+      </c>
+      <c r="F183" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F183" s="24" t="inlineStr">
+      <c r="G183" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G183" s="27" t="inlineStr"/>
-      <c r="H183" s="26" t="n"/>
+      <c r="H183" s="27" t="inlineStr"/>
+      <c r="I183" s="26" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="24" t="n">
         <v>57</v>
       </c>
       <c r="B184" s="25">
-        <f>IF($E$3="","",$E$3+A184-1)</f>
+        <f>IF($B$3="","",$B$3+A184-1)</f>
         <v/>
       </c>
       <c r="C184" s="24" t="n">
@@ -6115,25 +7031,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E184" s="24" t="inlineStr">
+      <c r="E184" s="36" t="inlineStr">
+        <is>
+          <t>The spec sheet said one thing. The dirt said another.</t>
+        </is>
+      </c>
+      <c r="F184" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F184" s="24" t="inlineStr">
+      <c r="G184" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G184" s="27" t="inlineStr"/>
-      <c r="H184" s="26" t="n"/>
+      <c r="H184" s="27" t="inlineStr"/>
+      <c r="I184" s="26" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="24" t="n">
         <v>58</v>
       </c>
       <c r="B185" s="25">
-        <f>IF($E$3="","",$E$3+A185-1)</f>
+        <f>IF($B$3="","",$B$3+A185-1)</f>
         <v/>
       </c>
       <c r="C185" s="24" t="n">
@@ -6144,25 +7065,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E185" s="24" t="inlineStr">
+      <c r="E185" s="36" t="inlineStr">
+        <is>
+          <t>Two inches down and it's already shining.</t>
+        </is>
+      </c>
+      <c r="F185" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F185" s="24" t="inlineStr">
+      <c r="G185" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G185" s="27" t="inlineStr"/>
-      <c r="H185" s="26" t="n"/>
+      <c r="H185" s="27" t="inlineStr"/>
+      <c r="I185" s="26" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="24" t="n">
         <v>58</v>
       </c>
       <c r="B186" s="25">
-        <f>IF($E$3="","",$E$3+A186-1)</f>
+        <f>IF($B$3="","",$B$3+A186-1)</f>
         <v/>
       </c>
       <c r="C186" s="24" t="n">
@@ -6173,25 +7099,30 @@
           <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
-      <c r="E186" s="24" t="inlineStr">
+      <c r="E186" s="36" t="inlineStr">
+        <is>
+          <t>Let's find out if the scanner was right.</t>
+        </is>
+      </c>
+      <c r="F186" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F186" s="24" t="inlineStr">
+      <c r="G186" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G186" s="27" t="inlineStr"/>
-      <c r="H186" s="26" t="n"/>
+      <c r="H186" s="27" t="inlineStr"/>
+      <c r="I186" s="26" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="24" t="n">
         <v>58</v>
       </c>
       <c r="B187" s="25">
-        <f>IF($E$3="","",$E$3+A187-1)</f>
+        <f>IF($B$3="","",$B$3+A187-1)</f>
         <v/>
       </c>
       <c r="C187" s="24" t="n">
@@ -6202,25 +7133,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E187" s="24" t="inlineStr">
+      <c r="E187" s="36" t="inlineStr">
+        <is>
+          <t>Same ground, same target, two very different price tags.</t>
+        </is>
+      </c>
+      <c r="F187" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F187" s="24" t="inlineStr">
+      <c r="G187" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G187" s="27" t="inlineStr"/>
-      <c r="H187" s="26" t="n"/>
+      <c r="H187" s="27" t="inlineStr"/>
+      <c r="I187" s="26" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="24" t="n">
         <v>58</v>
       </c>
       <c r="B188" s="25">
-        <f>IF($E$3="","",$E$3+A188-1)</f>
+        <f>IF($B$3="","",$B$3+A188-1)</f>
         <v/>
       </c>
       <c r="C188" s="24" t="n">
@@ -6231,25 +7167,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E188" s="24" t="inlineStr">
+      <c r="E188" s="36" t="inlineStr">
+        <is>
+          <t>Your detector is telling you something. Here's what.</t>
+        </is>
+      </c>
+      <c r="F188" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F188" s="24" t="inlineStr">
+      <c r="G188" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G188" s="27" t="inlineStr"/>
-      <c r="H188" s="26" t="n"/>
+      <c r="H188" s="27" t="inlineStr"/>
+      <c r="I188" s="26" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="24" t="n">
         <v>59</v>
       </c>
       <c r="B189" s="25">
-        <f>IF($E$3="","",$E$3+A189-1)</f>
+        <f>IF($B$3="","",$B$3+A189-1)</f>
         <v/>
       </c>
       <c r="C189" s="24" t="n">
@@ -6260,25 +7201,30 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E189" s="24" t="inlineStr">
+      <c r="E189" s="36" t="inlineStr">
+        <is>
+          <t>Can it really punch through that? Honestly.</t>
+        </is>
+      </c>
+      <c r="F189" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F189" s="24" t="inlineStr">
+      <c r="G189" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G189" s="27" t="inlineStr"/>
-      <c r="H189" s="26" t="n"/>
+      <c r="H189" s="27" t="inlineStr"/>
+      <c r="I189" s="26" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="24" t="n">
         <v>59</v>
       </c>
       <c r="B190" s="25">
-        <f>IF($E$3="","",$E$3+A190-1)</f>
+        <f>IF($B$3="","",$B$3+A190-1)</f>
         <v/>
       </c>
       <c r="C190" s="24" t="n">
@@ -6289,25 +7235,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E190" s="24" t="inlineStr">
+      <c r="E190" s="36" t="inlineStr">
+        <is>
+          <t>Most people walk away from this sound. Don't.</t>
+        </is>
+      </c>
+      <c r="F190" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F190" s="24" t="inlineStr">
+      <c r="G190" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G190" s="27" t="inlineStr"/>
-      <c r="H190" s="26" t="n"/>
+      <c r="H190" s="27" t="inlineStr"/>
+      <c r="I190" s="26" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="24" t="n">
         <v>59</v>
       </c>
       <c r="B191" s="25">
-        <f>IF($E$3="","",$E$3+A191-1)</f>
+        <f>IF($B$3="","",$B$3+A191-1)</f>
         <v/>
       </c>
       <c r="C191" s="24" t="n">
@@ -6318,25 +7269,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E191" s="24" t="inlineStr">
+      <c r="E191" s="36" t="inlineStr">
+        <is>
+          <t>Before you spend $2,000, watch this.</t>
+        </is>
+      </c>
+      <c r="F191" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F191" s="24" t="inlineStr">
+      <c r="G191" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G191" s="27" t="inlineStr"/>
-      <c r="H191" s="26" t="n"/>
+      <c r="H191" s="27" t="inlineStr"/>
+      <c r="I191" s="26" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="24" t="n">
         <v>59</v>
       </c>
       <c r="B192" s="25">
-        <f>IF($E$3="","",$E$3+A192-1)</f>
+        <f>IF($B$3="","",$B$3+A192-1)</f>
         <v/>
       </c>
       <c r="C192" s="24" t="n">
@@ -6347,20 +7303,25 @@
           <t>05 Ring Recovery</t>
         </is>
       </c>
-      <c r="E192" s="24" t="inlineStr">
+      <c r="E192" s="36" t="inlineStr">
+        <is>
+          <t>This is the call every detectorist waits for.</t>
+        </is>
+      </c>
+      <c r="F192" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F192" s="24" t="inlineStr">
+      <c r="G192" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G192" s="27" t="inlineStr"/>
-      <c r="H192" s="32" t="inlineStr">
-        <is>
-          <t>Opportunistic — publish when it happens, never force it</t>
+      <c r="H192" s="27" t="inlineStr"/>
+      <c r="I192" s="32" t="inlineStr">
+        <is>
+          <t>Opportunistic — never force it</t>
         </is>
       </c>
     </row>
@@ -6369,7 +7330,7 @@
         <v>60</v>
       </c>
       <c r="B193" s="25">
-        <f>IF($E$3="","",$E$3+A193-1)</f>
+        <f>IF($B$3="","",$B$3+A193-1)</f>
         <v/>
       </c>
       <c r="C193" s="24" t="n">
@@ -6380,25 +7341,30 @@
           <t>09 Read the Tone</t>
         </is>
       </c>
-      <c r="E193" s="24" t="inlineStr">
+      <c r="E193" s="36" t="inlineStr">
+        <is>
+          <t>If you hear this, dig it.</t>
+        </is>
+      </c>
+      <c r="F193" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F193" s="24" t="inlineStr">
+      <c r="G193" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G193" s="27" t="inlineStr"/>
-      <c r="H193" s="26" t="n"/>
+      <c r="H193" s="27" t="inlineStr"/>
+      <c r="I193" s="26" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="24" t="n">
         <v>60</v>
       </c>
       <c r="B194" s="25">
-        <f>IF($E$3="","",$E$3+A194-1)</f>
+        <f>IF($B$3="","",$B$3+A194-1)</f>
         <v/>
       </c>
       <c r="C194" s="24" t="n">
@@ -6409,25 +7375,30 @@
           <t>12 Detector vs Detector</t>
         </is>
       </c>
-      <c r="E194" s="24" t="inlineStr">
+      <c r="E194" s="36" t="inlineStr">
+        <is>
+          <t>The cheaper one won. I did not expect that.</t>
+        </is>
+      </c>
+      <c r="F194" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F194" s="24" t="inlineStr">
+      <c r="G194" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G194" s="27" t="inlineStr"/>
-      <c r="H194" s="26" t="n"/>
+      <c r="H194" s="27" t="inlineStr"/>
+      <c r="I194" s="26" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="24" t="n">
         <v>60</v>
       </c>
       <c r="B195" s="25">
-        <f>IF($E$3="","",$E$3+A195-1)</f>
+        <f>IF($B$3="","",$B$3+A195-1)</f>
         <v/>
       </c>
       <c r="C195" s="24" t="n">
@@ -6438,25 +7409,30 @@
           <t>04 The Dig Reveal</t>
         </is>
       </c>
-      <c r="E195" s="24" t="inlineStr">
+      <c r="E195" s="36" t="inlineStr">
+        <is>
+          <t>That's not a bottle cap.</t>
+        </is>
+      </c>
+      <c r="F195" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F195" s="24" t="inlineStr">
+      <c r="G195" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G195" s="27" t="inlineStr"/>
-      <c r="H195" s="26" t="n"/>
+      <c r="H195" s="27" t="inlineStr"/>
+      <c r="I195" s="26" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="24" t="n">
         <v>60</v>
       </c>
       <c r="B196" s="25">
-        <f>IF($E$3="","",$E$3+A196-1)</f>
+        <f>IF($B$3="","",$B$3+A196-1)</f>
         <v/>
       </c>
       <c r="C196" s="24" t="n">
@@ -6467,51 +7443,70 @@
           <t>11 Myth Test</t>
         </is>
       </c>
-      <c r="E196" s="24" t="inlineStr">
+      <c r="E196" s="36" t="inlineStr">
+        <is>
+          <t>Everyone says you can't detect wet salt sand. Let's find out.</t>
+        </is>
+      </c>
+      <c r="F196" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="F196" s="24" t="inlineStr">
+      <c r="G196" s="24" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="G196" s="27" t="inlineStr"/>
-      <c r="H196" s="26" t="n"/>
+      <c r="H196" s="27" t="inlineStr"/>
+      <c r="I196" s="26" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>COVERAGE CHECK</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>COVERAGE CHECK</t>
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Meets 5-sample minimum?</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="6" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>Meets 5-sample minimum?</t>
-        </is>
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="B200" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C200" s="18">
+        <f>IF(B200&gt;=5,"Yes","NO — add slots")</f>
+        <v/>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>01 The Depth Duel</t>
+          <t>02 Ground Scanner Reveal</t>
         </is>
       </c>
       <c r="B201" s="19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C201" s="18">
         <f>IF(B201&gt;=5,"Yes","NO — add slots")</f>
@@ -6521,7 +7516,7 @@
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>02 Ground Scanner Reveal</t>
+          <t>03 You Pick the Spot</t>
         </is>
       </c>
       <c r="B202" s="19" t="n">
@@ -6535,11 +7530,11 @@
     <row r="203">
       <c r="A203" s="18" t="inlineStr">
         <is>
-          <t>03 You Pick the Spot</t>
+          <t>04 The Dig Reveal</t>
         </is>
       </c>
       <c r="B203" s="19" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C203" s="18">
         <f>IF(B203&gt;=5,"Yes","NO — add slots")</f>
@@ -6549,11 +7544,11 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>04 The Dig Reveal</t>
+          <t>05 Ring Recovery</t>
         </is>
       </c>
       <c r="B204" s="19" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C204" s="18">
         <f>IF(B204&gt;=5,"Yes","NO — add slots")</f>
@@ -6563,11 +7558,11 @@
     <row r="205">
       <c r="A205" s="18" t="inlineStr">
         <is>
-          <t>05 Ring Recovery</t>
+          <t>06 The Hour Haul</t>
         </is>
       </c>
       <c r="B205" s="19" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C205" s="18">
         <f>IF(B205&gt;=5,"Yes","NO — add slots")</f>
@@ -6577,11 +7572,11 @@
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>06 The Hour Haul</t>
+          <t>07 Gold Hunt</t>
         </is>
       </c>
       <c r="B206" s="19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C206" s="18">
         <f>IF(B206&gt;=5,"Yes","NO — add slots")</f>
@@ -6591,11 +7586,11 @@
     <row r="207">
       <c r="A207" s="18" t="inlineStr">
         <is>
-          <t>07 Gold Hunt</t>
+          <t>08 ASMR Restoration</t>
         </is>
       </c>
       <c r="B207" s="19" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C207" s="18">
         <f>IF(B207&gt;=5,"Yes","NO — add slots")</f>
@@ -6605,11 +7600,11 @@
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>08 ASMR Restoration</t>
+          <t>09 Read the Tone</t>
         </is>
       </c>
       <c r="B208" s="19" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C208" s="18">
         <f>IF(B208&gt;=5,"Yes","NO — add slots")</f>
@@ -6619,11 +7614,11 @@
     <row r="209">
       <c r="A209" s="18" t="inlineStr">
         <is>
-          <t>09 Read the Tone</t>
+          <t>10 Detectorist Reacts</t>
         </is>
       </c>
       <c r="B209" s="19" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C209" s="18">
         <f>IF(B209&gt;=5,"Yes","NO — add slots")</f>
@@ -6633,11 +7628,11 @@
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>10 Detectorist Reacts</t>
+          <t>11 Myth Test</t>
         </is>
       </c>
       <c r="B210" s="19" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C210" s="18">
         <f>IF(B210&gt;=5,"Yes","NO — add slots")</f>
@@ -6647,60 +7642,41 @@
     <row r="211">
       <c r="A211" s="18" t="inlineStr">
         <is>
-          <t>11 Myth Test</t>
+          <t>12 Detector vs Detector</t>
         </is>
       </c>
       <c r="B211" s="19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C211" s="18">
         <f>IF(B211&gt;=5,"Yes","NO — add slots")</f>
         <v/>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="18" t="inlineStr">
-        <is>
-          <t>12 Detector vs Detector</t>
-        </is>
-      </c>
-      <c r="B212" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="C212" s="18">
-        <f>IF(B212&gt;=5,"Yes","NO — add slots")</f>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Total pieces</t>
+        </is>
+      </c>
+      <c r="B213" s="33">
+        <f>SUM(B200:B212)</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>Total pieces</t>
+          <t>Field shoot days needed</t>
         </is>
       </c>
       <c r="B214" s="33">
-        <f>SUM(B201:B213)</f>
+        <f>ROUNDUP(COUNTIF(F6:F196,"Field")/10,0)</f>
         <v/>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>x4 platforms = total uploads</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Field shoot days needed</t>
-        </is>
-      </c>
-      <c r="B215" s="33">
-        <f>ROUNDUP(COUNTIF(E6:E196,"Field")/10,0)</f>
-        <v/>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>Assumes ~10 usable pieces per field day — adjust once you know your real yield.</t>
+          <t>Assumes ~10 usable pieces per field day — adjust to your real yield.</t>
         </is>
       </c>
     </row>
@@ -6710,6 +7686,1171 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Hook Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The first three seconds decide reach. With no ad spend, the hook is the only reach lever you have. Add your own as you learn what lands — the plan cycles through these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>Hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>01 The Depth Duel</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>This $300 detector says there's nothing here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr"/>
+      <c r="B6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Same spot, same target. One of these finds it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr"/>
+      <c r="B7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>I buried this at four feet. Let's see which one screams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Your detector isn't broken. It's just shallow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>$300 versus $10,000, same patch of dirt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>The cheap one walked straight over it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Three detectors, one target, only one is honest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr"/>
+      <c r="B12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>If your detector goes quiet here, it's lying to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr"/>
+      <c r="B13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>This is why beginners quit. Watch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr"/>
+      <c r="B14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Everyone's detector missed this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>02 Ground Scanner Reveal</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>There's something two metres under this field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr"/>
+      <c r="B16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>The screen says metal. The ground says nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr"/>
+      <c r="B17" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>This is what underground actually looks like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr"/>
+      <c r="B18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>That red blob is eight feet down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr"/>
+      <c r="B19" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Most detectorists never see this screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr"/>
+      <c r="B20" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>The machine drew this before I touched a shovel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr"/>
+      <c r="B21" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Scan first, dig second. Here's why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr"/>
+      <c r="B22" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Something big is under here, and it isn't a pipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr"/>
+      <c r="B23" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>I scanned before I dug. Here's what it showed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr"/>
+      <c r="B24" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Let's find out if the scanner was right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>03 You Pick the Spot</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Comment a number. I'm digging whichever square wins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr"/>
+      <c r="B26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Nine squares. You choose, I dig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr"/>
+      <c r="B27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Pick one. I'll be back tomorrow with what's in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr"/>
+      <c r="B28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Half of you said square four. So square four it is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr"/>
+      <c r="B29" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>You picked it. Now I have to dig it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr"/>
+      <c r="B30" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Last time you chose wrong. Try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="B31" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Grid's marked. Your move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr"/>
+      <c r="B32" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Most comments wins. I dig at dawn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>04 The Dig Reveal</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>That tone means it's silver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr"/>
+      <c r="B34" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>I almost walked past this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr"/>
+      <c r="B35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Two inches down and it's already shining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr"/>
+      <c r="B36" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>That's not a bottle cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr"/>
+      <c r="B37" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Listen to that. That's a good one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr"/>
+      <c r="B38" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>Twelve years detecting and this still got me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr"/>
+      <c r="B39" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>The signal was screaming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr"/>
+      <c r="B40" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>Whatever this is, it's deep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr"/>
+      <c r="B41" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>I've never dug one this clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr"/>
+      <c r="B42" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Watch the dirt come off this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr"/>
+      <c r="B43" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Bottle cap. Bottle cap. Bottle cap. Oh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr"/>
+      <c r="B44" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>This ground's been hunted a thousand times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>05 Ring Recovery</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>She lost it in this lake eleven years ago.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr"/>
+      <c r="B46" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>He proposed with it. Then the tide took it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr"/>
+      <c r="B47" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Forty minutes of searching for something this small.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr"/>
+      <c r="B48" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>She'd already given up on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr"/>
+      <c r="B49" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>This is the call every detectorist waits for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr"/>
+      <c r="B50" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Twenty years married. Lost it in one afternoon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>06 The Hour Haul</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>One hour on this beach. Counter starts now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr"/>
+      <c r="B52" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Sixty minutes. Let's see what this sand is hiding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr"/>
+      <c r="B53" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>One hour, one detector, no cherry-picking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr"/>
+      <c r="B54" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Everything I find in an hour. Good and bad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr"/>
+      <c r="B55" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>An hour here after a storm. This should be good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr"/>
+      <c r="B56" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>How much can one hour actually pay?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr"/>
+      <c r="B57" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>Timer's on. Let's go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="inlineStr">
+        <is>
+          <t>07 Gold Hunt</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Third day on this creek. Today it finally paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr"/>
+      <c r="B59" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>That's gold. That's actually gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr"/>
+      <c r="B60" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Everyone said this ground was worked out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr"/>
+      <c r="B61" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>The pan doesn't lie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr"/>
+      <c r="B62" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Six hours for this, and worth every one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr"/>
+      <c r="B63" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>That colour in the scoop. You know the one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr"/>
+      <c r="B64" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>If this is what I think it is...</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="39" t="inlineStr">
+        <is>
+          <t>08 ASMR Restoration</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>Sixty years of dirt. Watch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr"/>
+      <c r="B66" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>You will not believe what's under this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr"/>
+      <c r="B67" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>No talking. Just cleaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr"/>
+      <c r="B68" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>Give it thirty seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr"/>
+      <c r="B69" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>This came out of the ground looking like a rock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr"/>
+      <c r="B70" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>Before and after, no filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr"/>
+      <c r="B71" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>The first shine is the best part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr"/>
+      <c r="B72" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Green to gold in three minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>09 Read the Tone</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>Most people walk away from this sound. Don't.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr"/>
+      <c r="B74" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>If you hear this, dig it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr"/>
+      <c r="B75" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>This tone costs beginners their best finds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr"/>
+      <c r="B76" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Iron or silver? Listen again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr"/>
+      <c r="B77" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>That flutter means it's sitting on edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr"/>
+      <c r="B78" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>One sound, two very different outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="inlineStr"/>
+      <c r="B79" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>Learn this tone and you'll double your finds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr"/>
+      <c r="B80" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>Your detector is telling you something. Here's what.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="inlineStr">
+        <is>
+          <t>10 Detectorist Reacts</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>He has no idea what he just dug up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr"/>
+      <c r="B82" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>She thinks that's junk. It isn't.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr"/>
+      <c r="B83" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>This might be the find of the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr"/>
+      <c r="B84" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>He nearly threw it back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr"/>
+      <c r="B85" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>Watch his face when he realises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr"/>
+      <c r="B86" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>I've been sent a hundred of these. This one's different.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr"/>
+      <c r="B87" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>That is not what he thinks it is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="39" t="inlineStr">
+        <is>
+          <t>11 Myth Test</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>Everyone says you can't detect wet salt sand. Let's find out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr"/>
+      <c r="B89" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>They told me this ground was dead. Testing that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr"/>
+      <c r="B90" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Does coil size actually matter? Real test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr"/>
+      <c r="B91" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>The rain myth, settled today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr"/>
+      <c r="B92" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>Everybody repeats this. Nobody's tested it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr"/>
+      <c r="B93" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>I hope I'm wrong about this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr"/>
+      <c r="B94" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>Can it really punch through that? Honestly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="39" t="inlineStr">
+        <is>
+          <t>12 Detector vs Detector</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>Same ground, same target, two very different price tags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr"/>
+      <c r="B96" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>Before you spend $2,000, watch this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr"/>
+      <c r="B97" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>The cheaper one won. I did not expect that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="inlineStr"/>
+      <c r="B98" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Which one would you actually buy?</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="18" t="inlineStr"/>
+      <c r="B99" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>Identical conditions, honest result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr"/>
+      <c r="B100" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>I tested both so you don't have to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr"/>
+      <c r="B101" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>The spec sheet said one thing. The dirt said another.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19260,7 +21401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19789,7 +21930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
